--- a/docs/oc-mensuales/articulos-de-aseo-e-higiene/ago-2026.xlsx
+++ b/docs/oc-mensuales/articulos-de-aseo-e-higiene/ago-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC ago-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC ago-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2013,7 +2013,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2745,7 +2745,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5429,7 +5429,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -5551,7 +5551,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5856,7 +5856,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6100,7 +6100,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6527,7 +6527,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -6832,7 +6832,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
@@ -6893,7 +6893,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -7015,7 +7015,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -7137,7 +7137,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -7320,7 +7320,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -7381,7 +7381,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
@@ -7442,7 +7442,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -7503,7 +7503,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -7518,7 +7518,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -7568,7 +7568,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -7690,7 +7690,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -7751,7 +7751,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -7812,7 +7812,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -7873,7 +7873,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -7934,7 +7934,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -7995,7 +7995,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -8056,7 +8056,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -8117,7 +8117,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -8178,7 +8178,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -8300,7 +8300,7 @@
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -8361,7 +8361,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -8422,7 +8422,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -8544,7 +8544,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -8605,7 +8605,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -8666,7 +8666,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -8727,7 +8727,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -8788,7 +8788,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -8849,7 +8849,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -8971,7 +8971,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -9032,7 +9032,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -9093,7 +9093,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -9154,7 +9154,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -9215,7 +9215,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -9337,7 +9337,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -9398,7 +9398,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -9459,7 +9459,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -9520,7 +9520,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -9581,7 +9581,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -9642,7 +9642,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -9764,7 +9764,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -9825,7 +9825,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -9886,7 +9886,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -10008,7 +10008,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -10069,7 +10069,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -10130,7 +10130,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -10191,7 +10191,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -10252,7 +10252,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -10313,7 +10313,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -10435,7 +10435,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -10496,7 +10496,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -10557,7 +10557,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -10618,7 +10618,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -10679,7 +10679,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -10740,7 +10740,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -10801,7 +10801,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -10862,7 +10862,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -10923,7 +10923,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -10984,7 +10984,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -11045,7 +11045,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -11106,7 +11106,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -11167,7 +11167,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -11228,7 +11228,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -11289,7 +11289,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -11350,7 +11350,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -11411,7 +11411,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -11472,7 +11472,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -11533,7 +11533,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -11594,7 +11594,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -11655,7 +11655,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -11716,7 +11716,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -11777,7 +11777,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -11838,7 +11838,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -11899,7 +11899,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -11960,7 +11960,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -12021,7 +12021,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -12082,7 +12082,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -12143,7 +12143,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -12204,7 +12204,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -12265,7 +12265,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -12448,7 +12448,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -12509,7 +12509,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -12570,7 +12570,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -12631,7 +12631,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -12692,7 +12692,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -12753,7 +12753,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -12814,7 +12814,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -12875,7 +12875,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -12936,7 +12936,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -12997,7 +12997,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -13058,7 +13058,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -13119,7 +13119,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -13180,7 +13180,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -13241,7 +13241,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -13485,7 +13485,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -13546,7 +13546,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -13607,7 +13607,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -13668,7 +13668,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -13729,7 +13729,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -13790,7 +13790,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -13912,7 +13912,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -13973,7 +13973,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -14034,7 +14034,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -14095,7 +14095,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -14156,7 +14156,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -14217,7 +14217,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -14278,7 +14278,7 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -14400,7 +14400,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -14461,7 +14461,7 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -14583,7 +14583,7 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I232" t="inlineStr">
@@ -14644,7 +14644,7 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -14705,7 +14705,7 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -14766,7 +14766,7 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -14827,7 +14827,7 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -14888,7 +14888,7 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -14949,7 +14949,7 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -15010,7 +15010,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -15071,7 +15071,7 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -15132,7 +15132,7 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -15193,7 +15193,7 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
@@ -15254,7 +15254,7 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -15376,7 +15376,7 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -15437,7 +15437,7 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -15498,7 +15498,7 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -15559,7 +15559,7 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -15620,7 +15620,7 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -15681,7 +15681,7 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -15742,7 +15742,7 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -15803,7 +15803,7 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
@@ -15864,7 +15864,7 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
@@ -15986,7 +15986,7 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -16047,7 +16047,7 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -16108,7 +16108,7 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
@@ -16169,7 +16169,7 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
@@ -16230,7 +16230,7 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
@@ -16291,7 +16291,7 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
@@ -16352,7 +16352,7 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
@@ -16413,7 +16413,7 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
@@ -16474,7 +16474,7 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
@@ -16535,7 +16535,7 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
@@ -16596,7 +16596,7 @@
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
@@ -16657,7 +16657,7 @@
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I266" t="inlineStr">
@@ -16718,7 +16718,7 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
@@ -16779,7 +16779,7 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -16840,7 +16840,7 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
@@ -16901,7 +16901,7 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
@@ -16962,7 +16962,7 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
@@ -17023,7 +17023,7 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
@@ -17084,7 +17084,7 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -17145,7 +17145,7 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -17206,7 +17206,7 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
@@ -17267,7 +17267,7 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
@@ -17389,7 +17389,7 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
@@ -17450,7 +17450,7 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
@@ -17511,7 +17511,7 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
@@ -17572,7 +17572,7 @@
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
@@ -17694,7 +17694,7 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
@@ -17755,7 +17755,7 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
@@ -17816,7 +17816,7 @@
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
@@ -17877,7 +17877,7 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -17938,7 +17938,7 @@
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I287" t="inlineStr">
@@ -17999,7 +17999,7 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -18060,7 +18060,7 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
@@ -18121,7 +18121,7 @@
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
@@ -18182,7 +18182,7 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -18243,7 +18243,7 @@
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
@@ -18304,7 +18304,7 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I293" t="inlineStr">
@@ -18365,7 +18365,7 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
@@ -18487,7 +18487,7 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
@@ -18548,7 +18548,7 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
@@ -18609,7 +18609,7 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
@@ -18670,7 +18670,7 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
@@ -18731,7 +18731,7 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -18792,7 +18792,7 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -18853,7 +18853,7 @@
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
@@ -18914,7 +18914,7 @@
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
@@ -18975,7 +18975,7 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
@@ -19036,7 +19036,7 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -19097,7 +19097,7 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -19158,7 +19158,7 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
@@ -19219,7 +19219,7 @@
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
@@ -19280,7 +19280,7 @@
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
@@ -19341,7 +19341,7 @@
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -19402,7 +19402,7 @@
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
@@ -19463,7 +19463,7 @@
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
@@ -19524,7 +19524,7 @@
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
@@ -19585,7 +19585,7 @@
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
@@ -19646,7 +19646,7 @@
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
@@ -19707,7 +19707,7 @@
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
@@ -19768,7 +19768,7 @@
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
@@ -19829,7 +19829,7 @@
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
@@ -19890,7 +19890,7 @@
       </c>
       <c r="H319" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I319" t="inlineStr">
@@ -19951,7 +19951,7 @@
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
@@ -20073,7 +20073,7 @@
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
@@ -20134,7 +20134,7 @@
       </c>
       <c r="H323" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I323" t="inlineStr">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
@@ -20317,7 +20317,7 @@
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
@@ -20378,7 +20378,7 @@
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
@@ -20439,7 +20439,7 @@
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
@@ -20500,7 +20500,7 @@
       </c>
       <c r="H329" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I329" t="inlineStr">
@@ -20561,7 +20561,7 @@
       </c>
       <c r="H330" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I330" t="inlineStr">
@@ -20622,7 +20622,7 @@
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
@@ -20683,7 +20683,7 @@
       </c>
       <c r="H332" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I332" t="inlineStr">
@@ -20744,7 +20744,7 @@
       </c>
       <c r="H333" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I333" t="inlineStr">
@@ -20805,7 +20805,7 @@
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
@@ -20866,7 +20866,7 @@
       </c>
       <c r="H335" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I335" t="inlineStr">
@@ -20927,7 +20927,7 @@
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
@@ -20988,7 +20988,7 @@
       </c>
       <c r="H337" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I337" t="inlineStr">
@@ -21049,7 +21049,7 @@
       </c>
       <c r="H338" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I338" t="inlineStr">
@@ -21110,7 +21110,7 @@
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
@@ -21171,7 +21171,7 @@
       </c>
       <c r="H340" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I340" t="inlineStr">
@@ -21232,7 +21232,7 @@
       </c>
       <c r="H341" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I341" t="inlineStr">
@@ -21293,7 +21293,7 @@
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
@@ -21354,7 +21354,7 @@
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
@@ -21415,7 +21415,7 @@
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
@@ -21476,7 +21476,7 @@
       </c>
       <c r="H345" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I345" t="inlineStr">
@@ -21598,7 +21598,7 @@
       </c>
       <c r="H347" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I347" t="inlineStr">
@@ -21659,7 +21659,7 @@
       </c>
       <c r="H348" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I348" t="inlineStr">
@@ -21720,7 +21720,7 @@
       </c>
       <c r="H349" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I349" t="inlineStr">
@@ -21842,7 +21842,7 @@
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
@@ -21903,7 +21903,7 @@
       </c>
       <c r="H352" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I352" t="inlineStr">
@@ -21964,7 +21964,7 @@
       </c>
       <c r="H353" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I353" t="inlineStr">
@@ -22025,7 +22025,7 @@
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
@@ -22086,7 +22086,7 @@
       </c>
       <c r="H355" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I355" t="inlineStr">
@@ -22147,7 +22147,7 @@
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I356" t="inlineStr">
@@ -22208,7 +22208,7 @@
       </c>
       <c r="H357" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I357" t="inlineStr">
@@ -22269,7 +22269,7 @@
       </c>
       <c r="H358" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I358" t="inlineStr">
@@ -22330,7 +22330,7 @@
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I359" t="inlineStr">
@@ -22391,7 +22391,7 @@
       </c>
       <c r="H360" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I360" t="inlineStr">
@@ -22513,7 +22513,7 @@
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I362" t="inlineStr">
@@ -22574,7 +22574,7 @@
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I363" t="inlineStr">
@@ -22635,7 +22635,7 @@
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I364" t="inlineStr">
@@ -22696,7 +22696,7 @@
       </c>
       <c r="H365" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I365" t="inlineStr">
@@ -22757,7 +22757,7 @@
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I366" t="inlineStr">
@@ -22818,7 +22818,7 @@
       </c>
       <c r="H367" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I367" t="inlineStr">
@@ -22879,7 +22879,7 @@
       </c>
       <c r="H368" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I368" t="inlineStr">
@@ -22940,7 +22940,7 @@
       </c>
       <c r="H369" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I369" t="inlineStr">
@@ -23001,7 +23001,7 @@
       </c>
       <c r="H370" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I370" t="inlineStr">
@@ -23062,7 +23062,7 @@
       </c>
       <c r="H371" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I371" t="inlineStr">
@@ -23123,7 +23123,7 @@
       </c>
       <c r="H372" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I372" t="inlineStr">
@@ -23184,7 +23184,7 @@
       </c>
       <c r="H373" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I373" t="inlineStr">
@@ -23245,7 +23245,7 @@
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I374" t="inlineStr">
@@ -23306,7 +23306,7 @@
       </c>
       <c r="H375" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I375" t="inlineStr">
@@ -23367,7 +23367,7 @@
       </c>
       <c r="H376" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I376" t="inlineStr">
@@ -23428,7 +23428,7 @@
       </c>
       <c r="H377" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I377" t="inlineStr">
@@ -23489,7 +23489,7 @@
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I378" t="inlineStr">
@@ -23550,7 +23550,7 @@
       </c>
       <c r="H379" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I379" t="inlineStr">
@@ -23611,7 +23611,7 @@
       </c>
       <c r="H380" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I380" t="inlineStr">
@@ -23733,7 +23733,7 @@
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I382" t="inlineStr">
@@ -23794,7 +23794,7 @@
       </c>
       <c r="H383" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I383" t="inlineStr">
@@ -23855,7 +23855,7 @@
       </c>
       <c r="H384" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I384" t="inlineStr">
@@ -23916,7 +23916,7 @@
       </c>
       <c r="H385" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I385" t="inlineStr">
@@ -23977,7 +23977,7 @@
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I386" t="inlineStr">
@@ -24038,7 +24038,7 @@
       </c>
       <c r="H387" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I387" t="inlineStr">
@@ -24160,7 +24160,7 @@
       </c>
       <c r="H389" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I389" t="inlineStr">
@@ -24221,7 +24221,7 @@
       </c>
       <c r="H390" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I390" t="inlineStr">
@@ -24282,7 +24282,7 @@
       </c>
       <c r="H391" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I391" t="inlineStr">
@@ -24343,7 +24343,7 @@
       </c>
       <c r="H392" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I392" t="inlineStr">
@@ -24404,7 +24404,7 @@
       </c>
       <c r="H393" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I393" t="inlineStr">
@@ -24465,7 +24465,7 @@
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I394" t="inlineStr">
@@ -24526,7 +24526,7 @@
       </c>
       <c r="H395" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I395" t="inlineStr">
@@ -24587,7 +24587,7 @@
       </c>
       <c r="H396" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I396" t="inlineStr">
@@ -24648,7 +24648,7 @@
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I397" t="inlineStr">
@@ -24709,7 +24709,7 @@
       </c>
       <c r="H398" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I398" t="inlineStr">
@@ -24770,7 +24770,7 @@
       </c>
       <c r="H399" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I399" t="inlineStr">
@@ -24831,7 +24831,7 @@
       </c>
       <c r="H400" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I400" t="inlineStr">
@@ -24892,7 +24892,7 @@
       </c>
       <c r="H401" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I401" t="inlineStr">
@@ -24953,7 +24953,7 @@
       </c>
       <c r="H402" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I402" t="inlineStr">
@@ -25014,7 +25014,7 @@
       </c>
       <c r="H403" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I403" t="inlineStr">
@@ -25075,7 +25075,7 @@
       </c>
       <c r="H404" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I404" t="inlineStr">
@@ -25136,7 +25136,7 @@
       </c>
       <c r="H405" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I405" t="inlineStr">
@@ -25197,7 +25197,7 @@
       </c>
       <c r="H406" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I406" t="inlineStr">
@@ -25258,7 +25258,7 @@
       </c>
       <c r="H407" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I407" t="inlineStr">
@@ -25319,7 +25319,7 @@
       </c>
       <c r="H408" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I408" t="inlineStr">
@@ -25380,7 +25380,7 @@
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I409" t="inlineStr">
@@ -25441,7 +25441,7 @@
       </c>
       <c r="H410" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I410" t="inlineStr">
@@ -25502,7 +25502,7 @@
       </c>
       <c r="H411" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I411" t="inlineStr">
@@ -25563,7 +25563,7 @@
       </c>
       <c r="H412" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I412" t="inlineStr">
@@ -25624,7 +25624,7 @@
       </c>
       <c r="H413" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I413" t="inlineStr">
@@ -25685,7 +25685,7 @@
       </c>
       <c r="H414" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I414" t="inlineStr">
@@ -25746,7 +25746,7 @@
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I415" t="inlineStr">
@@ -25807,7 +25807,7 @@
       </c>
       <c r="H416" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I416" t="inlineStr">
@@ -25868,7 +25868,7 @@
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I417" t="inlineStr">
@@ -25929,7 +25929,7 @@
       </c>
       <c r="H418" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I418" t="inlineStr">
@@ -25990,7 +25990,7 @@
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I419" t="inlineStr">
@@ -26051,7 +26051,7 @@
       </c>
       <c r="H420" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I420" t="inlineStr">
@@ -26112,7 +26112,7 @@
       </c>
       <c r="H421" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I421" t="inlineStr">
@@ -26173,7 +26173,7 @@
       </c>
       <c r="H422" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I422" t="inlineStr">
@@ -26234,7 +26234,7 @@
       </c>
       <c r="H423" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I423" t="inlineStr">
@@ -26356,7 +26356,7 @@
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I425" t="inlineStr">
@@ -26478,7 +26478,7 @@
       </c>
       <c r="H427" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I427" t="inlineStr">
@@ -26539,7 +26539,7 @@
       </c>
       <c r="H428" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I428" t="inlineStr">
@@ -26600,7 +26600,7 @@
       </c>
       <c r="H429" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I429" t="inlineStr">
@@ -26661,7 +26661,7 @@
       </c>
       <c r="H430" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I430" t="inlineStr">
@@ -26722,7 +26722,7 @@
       </c>
       <c r="H431" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I431" t="inlineStr">
@@ -26783,7 +26783,7 @@
       </c>
       <c r="H432" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I432" t="inlineStr">
@@ -26844,7 +26844,7 @@
       </c>
       <c r="H433" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I433" t="inlineStr">
@@ -26905,7 +26905,7 @@
       </c>
       <c r="H434" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I434" t="inlineStr">
@@ -26966,7 +26966,7 @@
       </c>
       <c r="H435" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I435" t="inlineStr">
@@ -27027,7 +27027,7 @@
       </c>
       <c r="H436" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I436" t="inlineStr">
@@ -27088,7 +27088,7 @@
       </c>
       <c r="H437" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I437" t="inlineStr">
@@ -27149,7 +27149,7 @@
       </c>
       <c r="H438" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I438" t="inlineStr">
@@ -27210,7 +27210,7 @@
       </c>
       <c r="H439" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I439" t="inlineStr">
@@ -27271,7 +27271,7 @@
       </c>
       <c r="H440" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I440" t="inlineStr">
@@ -27332,7 +27332,7 @@
       </c>
       <c r="H441" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I441" t="inlineStr">
@@ -27393,7 +27393,7 @@
       </c>
       <c r="H442" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I442" t="inlineStr">
@@ -27454,7 +27454,7 @@
       </c>
       <c r="H443" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I443" t="inlineStr">
@@ -27515,7 +27515,7 @@
       </c>
       <c r="H444" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I444" t="inlineStr">
@@ -27576,7 +27576,7 @@
       </c>
       <c r="H445" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I445" t="inlineStr">
@@ -27637,7 +27637,7 @@
       </c>
       <c r="H446" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I446" t="inlineStr">
@@ -27698,7 +27698,7 @@
       </c>
       <c r="H447" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I447" t="inlineStr">
@@ -27759,7 +27759,7 @@
       </c>
       <c r="H448" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I448" t="inlineStr">
@@ -27820,7 +27820,7 @@
       </c>
       <c r="H449" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I449" t="inlineStr">
@@ -27881,7 +27881,7 @@
       </c>
       <c r="H450" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I450" t="inlineStr">
@@ -27942,7 +27942,7 @@
       </c>
       <c r="H451" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I451" t="inlineStr">
@@ -28003,7 +28003,7 @@
       </c>
       <c r="H452" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I452" t="inlineStr">
@@ -28064,7 +28064,7 @@
       </c>
       <c r="H453" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I453" t="inlineStr">
@@ -28125,7 +28125,7 @@
       </c>
       <c r="H454" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I454" t="inlineStr">
@@ -28186,7 +28186,7 @@
       </c>
       <c r="H455" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I455" t="inlineStr">
@@ -28247,7 +28247,7 @@
       </c>
       <c r="H456" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I456" t="inlineStr">
@@ -28308,7 +28308,7 @@
       </c>
       <c r="H457" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I457" t="inlineStr">
@@ -28369,7 +28369,7 @@
       </c>
       <c r="H458" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I458" t="inlineStr">
@@ -28430,7 +28430,7 @@
       </c>
       <c r="H459" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I459" t="inlineStr">
@@ -28491,7 +28491,7 @@
       </c>
       <c r="H460" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I460" t="inlineStr">
@@ -28613,7 +28613,7 @@
       </c>
       <c r="H462" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I462" t="inlineStr">
@@ -28674,7 +28674,7 @@
       </c>
       <c r="H463" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I463" t="inlineStr">
@@ -28735,7 +28735,7 @@
       </c>
       <c r="H464" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I464" t="inlineStr">
@@ -28796,7 +28796,7 @@
       </c>
       <c r="H465" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I465" t="inlineStr">
@@ -28857,7 +28857,7 @@
       </c>
       <c r="H466" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I466" t="inlineStr">
@@ -28918,7 +28918,7 @@
       </c>
       <c r="H467" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I467" t="inlineStr">
@@ -28979,7 +28979,7 @@
       </c>
       <c r="H468" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I468" t="inlineStr">
@@ -29040,7 +29040,7 @@
       </c>
       <c r="H469" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I469" t="inlineStr">
@@ -29101,7 +29101,7 @@
       </c>
       <c r="H470" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I470" t="inlineStr">
@@ -29162,7 +29162,7 @@
       </c>
       <c r="H471" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I471" t="inlineStr">
@@ -29284,7 +29284,7 @@
       </c>
       <c r="H473" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I473" t="inlineStr">
@@ -29345,7 +29345,7 @@
       </c>
       <c r="H474" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I474" t="inlineStr">
@@ -29406,7 +29406,7 @@
       </c>
       <c r="H475" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I475" t="inlineStr">
@@ -29467,7 +29467,7 @@
       </c>
       <c r="H476" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I476" t="inlineStr">
@@ -29528,7 +29528,7 @@
       </c>
       <c r="H477" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I477" t="inlineStr">
@@ -29589,7 +29589,7 @@
       </c>
       <c r="H478" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I478" t="inlineStr">
@@ -29711,7 +29711,7 @@
       </c>
       <c r="H480" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I480" t="inlineStr">
@@ -29772,7 +29772,7 @@
       </c>
       <c r="H481" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I481" t="inlineStr">
@@ -29833,7 +29833,7 @@
       </c>
       <c r="H482" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I482" t="inlineStr">
@@ -29894,7 +29894,7 @@
       </c>
       <c r="H483" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I483" t="inlineStr">
@@ -29955,7 +29955,7 @@
       </c>
       <c r="H484" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I484" t="inlineStr">
@@ -30016,7 +30016,7 @@
       </c>
       <c r="H485" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I485" t="inlineStr">
@@ -30077,7 +30077,7 @@
       </c>
       <c r="H486" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I486" t="inlineStr">
@@ -30138,7 +30138,7 @@
       </c>
       <c r="H487" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I487" t="inlineStr">
@@ -30199,7 +30199,7 @@
       </c>
       <c r="H488" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I488" t="inlineStr">
@@ -30260,7 +30260,7 @@
       </c>
       <c r="H489" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I489" t="inlineStr">
@@ -30321,7 +30321,7 @@
       </c>
       <c r="H490" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I490" t="inlineStr">
@@ -30382,7 +30382,7 @@
       </c>
       <c r="H491" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I491" t="inlineStr">
@@ -30443,7 +30443,7 @@
       </c>
       <c r="H492" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I492" t="inlineStr">
@@ -30504,7 +30504,7 @@
       </c>
       <c r="H493" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I493" t="inlineStr">
@@ -30565,7 +30565,7 @@
       </c>
       <c r="H494" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I494" t="inlineStr">
@@ -30626,7 +30626,7 @@
       </c>
       <c r="H495" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I495" t="inlineStr">
@@ -30687,7 +30687,7 @@
       </c>
       <c r="H496" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I496" t="inlineStr">
@@ -30748,7 +30748,7 @@
       </c>
       <c r="H497" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I497" t="inlineStr">
@@ -30870,7 +30870,7 @@
       </c>
       <c r="H499" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I499" t="inlineStr">
@@ -30931,7 +30931,7 @@
       </c>
       <c r="H500" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I500" t="inlineStr">
@@ -30992,7 +30992,7 @@
       </c>
       <c r="H501" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I501" t="inlineStr">
@@ -31175,7 +31175,7 @@
       </c>
       <c r="H504" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I504" t="inlineStr">
@@ -31297,7 +31297,7 @@
       </c>
       <c r="H506" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I506" t="inlineStr">
@@ -31358,7 +31358,7 @@
       </c>
       <c r="H507" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I507" t="inlineStr">
@@ -31419,7 +31419,7 @@
       </c>
       <c r="H508" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I508" t="inlineStr">
@@ -31480,7 +31480,7 @@
       </c>
       <c r="H509" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I509" t="inlineStr">
@@ -31541,7 +31541,7 @@
       </c>
       <c r="H510" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I510" t="inlineStr">
@@ -31602,7 +31602,7 @@
       </c>
       <c r="H511" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I511" t="inlineStr">
@@ -31663,7 +31663,7 @@
       </c>
       <c r="H512" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I512" t="inlineStr">
@@ -31724,7 +31724,7 @@
       </c>
       <c r="H513" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I513" t="inlineStr">
@@ -31785,7 +31785,7 @@
       </c>
       <c r="H514" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I514" t="inlineStr">
@@ -31846,7 +31846,7 @@
       </c>
       <c r="H515" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I515" t="inlineStr">
@@ -31907,7 +31907,7 @@
       </c>
       <c r="H516" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I516" t="inlineStr">
@@ -31968,7 +31968,7 @@
       </c>
       <c r="H517" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I517" t="inlineStr">
@@ -32029,7 +32029,7 @@
       </c>
       <c r="H518" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I518" t="inlineStr">
@@ -32090,7 +32090,7 @@
       </c>
       <c r="H519" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I519" t="inlineStr">
@@ -32151,7 +32151,7 @@
       </c>
       <c r="H520" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I520" t="inlineStr">
@@ -32212,7 +32212,7 @@
       </c>
       <c r="H521" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I521" t="inlineStr">
@@ -32273,7 +32273,7 @@
       </c>
       <c r="H522" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I522" t="inlineStr">
@@ -32334,7 +32334,7 @@
       </c>
       <c r="H523" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I523" t="inlineStr">
@@ -32395,7 +32395,7 @@
       </c>
       <c r="H524" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I524" t="inlineStr">
@@ -32456,7 +32456,7 @@
       </c>
       <c r="H525" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I525" t="inlineStr">
@@ -32578,7 +32578,7 @@
       </c>
       <c r="H527" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I527" t="inlineStr">
@@ -32639,7 +32639,7 @@
       </c>
       <c r="H528" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I528" t="inlineStr">
@@ -32700,7 +32700,7 @@
       </c>
       <c r="H529" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I529" t="inlineStr">
@@ -32761,7 +32761,7 @@
       </c>
       <c r="H530" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I530" t="inlineStr">
@@ -32883,7 +32883,7 @@
       </c>
       <c r="H532" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I532" t="inlineStr">
@@ -32944,7 +32944,7 @@
       </c>
       <c r="H533" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I533" t="inlineStr">
@@ -33005,7 +33005,7 @@
       </c>
       <c r="H534" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I534" t="inlineStr">
@@ -33066,7 +33066,7 @@
       </c>
       <c r="H535" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I535" t="inlineStr">
@@ -33188,7 +33188,7 @@
       </c>
       <c r="H537" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I537" t="inlineStr">
@@ -33249,7 +33249,7 @@
       </c>
       <c r="H538" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I538" t="inlineStr">
@@ -33310,7 +33310,7 @@
       </c>
       <c r="H539" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I539" t="inlineStr">
@@ -33371,7 +33371,7 @@
       </c>
       <c r="H540" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I540" t="inlineStr">
@@ -33432,7 +33432,7 @@
       </c>
       <c r="H541" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I541" t="inlineStr">
@@ -33554,7 +33554,7 @@
       </c>
       <c r="H543" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I543" t="inlineStr">
@@ -33615,7 +33615,7 @@
       </c>
       <c r="H544" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I544" t="inlineStr">
@@ -33676,7 +33676,7 @@
       </c>
       <c r="H545" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I545" t="inlineStr">
@@ -33737,7 +33737,7 @@
       </c>
       <c r="H546" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I546" t="inlineStr">
@@ -33798,7 +33798,7 @@
       </c>
       <c r="H547" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I547" t="inlineStr">
@@ -33859,7 +33859,7 @@
       </c>
       <c r="H548" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I548" t="inlineStr">
@@ -33920,7 +33920,7 @@
       </c>
       <c r="H549" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I549" t="inlineStr">
@@ -33981,7 +33981,7 @@
       </c>
       <c r="H550" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I550" t="inlineStr">
@@ -34042,7 +34042,7 @@
       </c>
       <c r="H551" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I551" t="inlineStr">
@@ -34164,7 +34164,7 @@
       </c>
       <c r="H553" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I553" t="inlineStr">
@@ -34225,7 +34225,7 @@
       </c>
       <c r="H554" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I554" t="inlineStr">
@@ -34286,7 +34286,7 @@
       </c>
       <c r="H555" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I555" t="inlineStr">
@@ -34347,7 +34347,7 @@
       </c>
       <c r="H556" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I556" t="inlineStr">
@@ -34408,7 +34408,7 @@
       </c>
       <c r="H557" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I557" t="inlineStr">
@@ -34469,7 +34469,7 @@
       </c>
       <c r="H558" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I558" t="inlineStr">
@@ -34530,7 +34530,7 @@
       </c>
       <c r="H559" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I559" t="inlineStr">
@@ -34591,7 +34591,7 @@
       </c>
       <c r="H560" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I560" t="inlineStr">
@@ -34652,7 +34652,7 @@
       </c>
       <c r="H561" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I561" t="inlineStr">
@@ -34713,7 +34713,7 @@
       </c>
       <c r="H562" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I562" t="inlineStr">
@@ -34774,7 +34774,7 @@
       </c>
       <c r="H563" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I563" t="inlineStr">
@@ -34835,7 +34835,7 @@
       </c>
       <c r="H564" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I564" t="inlineStr">
@@ -34896,7 +34896,7 @@
       </c>
       <c r="H565" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I565" t="inlineStr">
@@ -34957,7 +34957,7 @@
       </c>
       <c r="H566" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I566" t="inlineStr">
@@ -35018,7 +35018,7 @@
       </c>
       <c r="H567" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I567" t="inlineStr">
@@ -35079,7 +35079,7 @@
       </c>
       <c r="H568" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I568" t="inlineStr">
@@ -35140,7 +35140,7 @@
       </c>
       <c r="H569" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I569" t="inlineStr">
@@ -35201,7 +35201,7 @@
       </c>
       <c r="H570" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I570" t="inlineStr">
@@ -35262,7 +35262,7 @@
       </c>
       <c r="H571" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I571" t="inlineStr">
@@ -35323,7 +35323,7 @@
       </c>
       <c r="H572" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I572" t="inlineStr">
@@ -35384,7 +35384,7 @@
       </c>
       <c r="H573" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I573" t="inlineStr">
@@ -35445,7 +35445,7 @@
       </c>
       <c r="H574" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I574" t="inlineStr">
@@ -35506,7 +35506,7 @@
       </c>
       <c r="H575" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I575" t="inlineStr">
@@ -35567,7 +35567,7 @@
       </c>
       <c r="H576" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I576" t="inlineStr">
@@ -35628,7 +35628,7 @@
       </c>
       <c r="H577" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I577" t="inlineStr">
@@ -35689,7 +35689,7 @@
       </c>
       <c r="H578" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I578" t="inlineStr">
@@ -35750,7 +35750,7 @@
       </c>
       <c r="H579" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I579" t="inlineStr">
@@ -35811,7 +35811,7 @@
       </c>
       <c r="H580" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I580" t="inlineStr">
@@ -35872,7 +35872,7 @@
       </c>
       <c r="H581" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I581" t="inlineStr">
@@ -35933,7 +35933,7 @@
       </c>
       <c r="H582" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I582" t="inlineStr">
@@ -35994,7 +35994,7 @@
       </c>
       <c r="H583" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I583" t="inlineStr">
@@ -36055,7 +36055,7 @@
       </c>
       <c r="H584" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I584" t="inlineStr">
@@ -36116,7 +36116,7 @@
       </c>
       <c r="H585" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I585" t="inlineStr">
@@ -36177,7 +36177,7 @@
       </c>
       <c r="H586" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I586" t="inlineStr">
@@ -36238,7 +36238,7 @@
       </c>
       <c r="H587" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I587" t="inlineStr">
@@ -36299,7 +36299,7 @@
       </c>
       <c r="H588" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I588" t="inlineStr">
@@ -36360,7 +36360,7 @@
       </c>
       <c r="H589" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I589" t="inlineStr">
@@ -36421,7 +36421,7 @@
       </c>
       <c r="H590" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I590" t="inlineStr">
@@ -36482,7 +36482,7 @@
       </c>
       <c r="H591" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I591" t="inlineStr">
@@ -36604,7 +36604,7 @@
       </c>
       <c r="H593" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I593" t="inlineStr">
@@ -36665,7 +36665,7 @@
       </c>
       <c r="H594" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I594" t="inlineStr">
@@ -36726,7 +36726,7 @@
       </c>
       <c r="H595" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I595" t="inlineStr">
@@ -36787,7 +36787,7 @@
       </c>
       <c r="H596" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I596" t="inlineStr">
@@ -36909,7 +36909,7 @@
       </c>
       <c r="H598" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I598" t="inlineStr">
@@ -36970,7 +36970,7 @@
       </c>
       <c r="H599" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I599" t="inlineStr">
@@ -37031,7 +37031,7 @@
       </c>
       <c r="H600" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I600" t="inlineStr">
@@ -37092,7 +37092,7 @@
       </c>
       <c r="H601" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I601" t="inlineStr">
@@ -37153,7 +37153,7 @@
       </c>
       <c r="H602" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I602" t="inlineStr">
@@ -37214,7 +37214,7 @@
       </c>
       <c r="H603" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I603" t="inlineStr">
@@ -37275,7 +37275,7 @@
       </c>
       <c r="H604" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I604" t="inlineStr">
@@ -37336,7 +37336,7 @@
       </c>
       <c r="H605" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I605" t="inlineStr">
@@ -37397,7 +37397,7 @@
       </c>
       <c r="H606" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I606" t="inlineStr">
@@ -37458,7 +37458,7 @@
       </c>
       <c r="H607" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I607" t="inlineStr">
@@ -37519,7 +37519,7 @@
       </c>
       <c r="H608" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I608" t="inlineStr">
@@ -37580,7 +37580,7 @@
       </c>
       <c r="H609" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I609" t="inlineStr">
@@ -37641,7 +37641,7 @@
       </c>
       <c r="H610" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I610" t="inlineStr">
@@ -37702,7 +37702,7 @@
       </c>
       <c r="H611" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I611" t="inlineStr">
@@ -37763,7 +37763,7 @@
       </c>
       <c r="H612" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I612" t="inlineStr">
@@ -37885,7 +37885,7 @@
       </c>
       <c r="H614" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I614" t="inlineStr">
@@ -37946,7 +37946,7 @@
       </c>
       <c r="H615" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I615" t="inlineStr">
@@ -38007,7 +38007,7 @@
       </c>
       <c r="H616" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I616" t="inlineStr">
@@ -38068,7 +38068,7 @@
       </c>
       <c r="H617" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I617" t="inlineStr">
@@ -38129,7 +38129,7 @@
       </c>
       <c r="H618" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I618" t="inlineStr">
@@ -38190,7 +38190,7 @@
       </c>
       <c r="H619" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I619" t="inlineStr">
@@ -38251,7 +38251,7 @@
       </c>
       <c r="H620" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I620" t="inlineStr">
@@ -38312,7 +38312,7 @@
       </c>
       <c r="H621" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I621" t="inlineStr">
@@ -38373,7 +38373,7 @@
       </c>
       <c r="H622" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I622" t="inlineStr">
@@ -38434,7 +38434,7 @@
       </c>
       <c r="H623" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I623" t="inlineStr">
@@ -38495,7 +38495,7 @@
       </c>
       <c r="H624" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I624" t="inlineStr">
@@ -38556,7 +38556,7 @@
       </c>
       <c r="H625" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I625" t="inlineStr">
@@ -38617,7 +38617,7 @@
       </c>
       <c r="H626" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I626" t="inlineStr">
@@ -38678,7 +38678,7 @@
       </c>
       <c r="H627" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I627" t="inlineStr">
@@ -38739,7 +38739,7 @@
       </c>
       <c r="H628" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I628" t="inlineStr">
@@ -38800,7 +38800,7 @@
       </c>
       <c r="H629" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I629" t="inlineStr">
@@ -38861,7 +38861,7 @@
       </c>
       <c r="H630" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I630" t="inlineStr">
@@ -38983,7 +38983,7 @@
       </c>
       <c r="H632" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I632" t="inlineStr">
@@ -39044,7 +39044,7 @@
       </c>
       <c r="H633" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I633" t="inlineStr">
@@ -39105,7 +39105,7 @@
       </c>
       <c r="H634" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I634" t="inlineStr">
@@ -39166,7 +39166,7 @@
       </c>
       <c r="H635" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I635" t="inlineStr">
@@ -39227,7 +39227,7 @@
       </c>
       <c r="H636" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I636" t="inlineStr">
@@ -39288,7 +39288,7 @@
       </c>
       <c r="H637" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I637" t="inlineStr">
@@ -39349,7 +39349,7 @@
       </c>
       <c r="H638" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I638" t="inlineStr">
@@ -39410,7 +39410,7 @@
       </c>
       <c r="H639" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I639" t="inlineStr">
@@ -39471,7 +39471,7 @@
       </c>
       <c r="H640" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I640" t="inlineStr">
@@ -39532,7 +39532,7 @@
       </c>
       <c r="H641" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I641" t="inlineStr">
@@ -39654,7 +39654,7 @@
       </c>
       <c r="H643" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I643" t="inlineStr">
@@ -39776,7 +39776,7 @@
       </c>
       <c r="H645" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I645" t="inlineStr">
@@ -39837,7 +39837,7 @@
       </c>
       <c r="H646" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I646" t="inlineStr">
@@ -39898,7 +39898,7 @@
       </c>
       <c r="H647" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I647" t="inlineStr">
@@ -39959,7 +39959,7 @@
       </c>
       <c r="H648" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I648" t="inlineStr">
@@ -40081,7 +40081,7 @@
       </c>
       <c r="H650" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I650" t="inlineStr">
@@ -40142,7 +40142,7 @@
       </c>
       <c r="H651" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I651" t="inlineStr">
@@ -40264,7 +40264,7 @@
       </c>
       <c r="H653" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I653" t="inlineStr">
@@ -40325,7 +40325,7 @@
       </c>
       <c r="H654" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I654" t="inlineStr">
@@ -40447,7 +40447,7 @@
       </c>
       <c r="H656" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I656" t="inlineStr">
@@ -40508,7 +40508,7 @@
       </c>
       <c r="H657" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I657" t="inlineStr">
@@ -40569,7 +40569,7 @@
       </c>
       <c r="H658" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I658" t="inlineStr">
@@ -40630,7 +40630,7 @@
       </c>
       <c r="H659" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I659" t="inlineStr">
@@ -40752,7 +40752,7 @@
       </c>
       <c r="H661" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I661" t="inlineStr">
@@ -40813,7 +40813,7 @@
       </c>
       <c r="H662" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I662" t="inlineStr">
@@ -40874,7 +40874,7 @@
       </c>
       <c r="H663" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I663" t="inlineStr">
@@ -40935,7 +40935,7 @@
       </c>
       <c r="H664" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I664" t="inlineStr">
@@ -40996,7 +40996,7 @@
       </c>
       <c r="H665" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I665" t="inlineStr">
@@ -41057,7 +41057,7 @@
       </c>
       <c r="H666" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I666" t="inlineStr">
@@ -41118,7 +41118,7 @@
       </c>
       <c r="H667" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I667" t="inlineStr">
@@ -41179,7 +41179,7 @@
       </c>
       <c r="H668" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I668" t="inlineStr">
@@ -41240,7 +41240,7 @@
       </c>
       <c r="H669" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I669" t="inlineStr">
@@ -41301,7 +41301,7 @@
       </c>
       <c r="H670" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I670" t="inlineStr">
@@ -41362,7 +41362,7 @@
       </c>
       <c r="H671" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I671" t="inlineStr">
@@ -41423,7 +41423,7 @@
       </c>
       <c r="H672" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I672" t="inlineStr">
@@ -41484,7 +41484,7 @@
       </c>
       <c r="H673" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I673" t="inlineStr">
@@ -41606,7 +41606,7 @@
       </c>
       <c r="H675" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I675" t="inlineStr">
@@ -41667,7 +41667,7 @@
       </c>
       <c r="H676" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I676" t="inlineStr">
@@ -41728,7 +41728,7 @@
       </c>
       <c r="H677" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I677" t="inlineStr">
@@ -41789,7 +41789,7 @@
       </c>
       <c r="H678" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I678" t="inlineStr">
@@ -41850,7 +41850,7 @@
       </c>
       <c r="H679" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I679" t="inlineStr">
@@ -41911,7 +41911,7 @@
       </c>
       <c r="H680" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I680" t="inlineStr">
@@ -42033,7 +42033,7 @@
       </c>
       <c r="H682" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I682" t="inlineStr">
@@ -42094,7 +42094,7 @@
       </c>
       <c r="H683" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I683" t="inlineStr">
@@ -42155,7 +42155,7 @@
       </c>
       <c r="H684" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I684" t="inlineStr">
@@ -42216,7 +42216,7 @@
       </c>
       <c r="H685" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I685" t="inlineStr">
@@ -42277,7 +42277,7 @@
       </c>
       <c r="H686" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I686" t="inlineStr">
@@ -42338,7 +42338,7 @@
       </c>
       <c r="H687" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I687" t="inlineStr">
@@ -42399,7 +42399,7 @@
       </c>
       <c r="H688" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I688" t="inlineStr">
@@ -42521,7 +42521,7 @@
       </c>
       <c r="H690" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I690" t="inlineStr">
@@ -42582,7 +42582,7 @@
       </c>
       <c r="H691" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I691" t="inlineStr">
@@ -42643,7 +42643,7 @@
       </c>
       <c r="H692" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I692" t="inlineStr">
@@ -42765,7 +42765,7 @@
       </c>
       <c r="H694" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I694" t="inlineStr">
@@ -42826,7 +42826,7 @@
       </c>
       <c r="H695" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I695" t="inlineStr">
@@ -42887,7 +42887,7 @@
       </c>
       <c r="H696" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I696" t="inlineStr">
@@ -42948,7 +42948,7 @@
       </c>
       <c r="H697" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I697" t="inlineStr">
@@ -43070,7 +43070,7 @@
       </c>
       <c r="H699" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I699" t="inlineStr">
@@ -43131,7 +43131,7 @@
       </c>
       <c r="H700" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I700" t="inlineStr">
@@ -43192,7 +43192,7 @@
       </c>
       <c r="H701" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I701" t="inlineStr">
@@ -43253,7 +43253,7 @@
       </c>
       <c r="H702" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I702" t="inlineStr">
@@ -43314,7 +43314,7 @@
       </c>
       <c r="H703" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I703" t="inlineStr">
@@ -43375,7 +43375,7 @@
       </c>
       <c r="H704" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I704" t="inlineStr">
@@ -43436,7 +43436,7 @@
       </c>
       <c r="H705" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I705" t="inlineStr">
@@ -43497,7 +43497,7 @@
       </c>
       <c r="H706" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I706" t="inlineStr">
@@ -43558,7 +43558,7 @@
       </c>
       <c r="H707" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I707" t="inlineStr">
@@ -43619,7 +43619,7 @@
       </c>
       <c r="H708" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I708" t="inlineStr">
@@ -43680,7 +43680,7 @@
       </c>
       <c r="H709" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I709" t="inlineStr">
@@ -43741,7 +43741,7 @@
       </c>
       <c r="H710" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I710" t="inlineStr">
@@ -43802,7 +43802,7 @@
       </c>
       <c r="H711" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I711" t="inlineStr">
@@ -43863,7 +43863,7 @@
       </c>
       <c r="H712" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I712" t="inlineStr">
@@ -43924,7 +43924,7 @@
       </c>
       <c r="H713" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I713" t="inlineStr">
@@ -43985,7 +43985,7 @@
       </c>
       <c r="H714" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I714" t="inlineStr">
@@ -44046,7 +44046,7 @@
       </c>
       <c r="H715" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I715" t="inlineStr">
@@ -44107,7 +44107,7 @@
       </c>
       <c r="H716" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I716" t="inlineStr">
@@ -44168,7 +44168,7 @@
       </c>
       <c r="H717" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I717" t="inlineStr">
@@ -44229,7 +44229,7 @@
       </c>
       <c r="H718" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I718" t="inlineStr">
@@ -44290,7 +44290,7 @@
       </c>
       <c r="H719" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I719" t="inlineStr">
@@ -44351,7 +44351,7 @@
       </c>
       <c r="H720" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I720" t="inlineStr">
@@ -44412,7 +44412,7 @@
       </c>
       <c r="H721" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I721" t="inlineStr">
@@ -44473,7 +44473,7 @@
       </c>
       <c r="H722" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I722" t="inlineStr">
@@ -44534,7 +44534,7 @@
       </c>
       <c r="H723" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I723" t="inlineStr">
@@ -44595,7 +44595,7 @@
       </c>
       <c r="H724" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I724" t="inlineStr">
@@ -44656,7 +44656,7 @@
       </c>
       <c r="H725" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I725" t="inlineStr">
@@ -44717,7 +44717,7 @@
       </c>
       <c r="H726" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I726" t="inlineStr">
@@ -44778,7 +44778,7 @@
       </c>
       <c r="H727" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I727" t="inlineStr">
@@ -44839,7 +44839,7 @@
       </c>
       <c r="H728" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I728" t="inlineStr">
@@ -44900,7 +44900,7 @@
       </c>
       <c r="H729" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I729" t="inlineStr">
@@ -44961,7 +44961,7 @@
       </c>
       <c r="H730" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I730" t="inlineStr">
@@ -45022,7 +45022,7 @@
       </c>
       <c r="H731" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I731" t="inlineStr">
@@ -45083,7 +45083,7 @@
       </c>
       <c r="H732" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I732" t="inlineStr">
@@ -45144,7 +45144,7 @@
       </c>
       <c r="H733" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I733" t="inlineStr">
@@ -45205,7 +45205,7 @@
       </c>
       <c r="H734" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I734" t="inlineStr">
@@ -45266,7 +45266,7 @@
       </c>
       <c r="H735" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I735" t="inlineStr">
@@ -45327,7 +45327,7 @@
       </c>
       <c r="H736" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I736" t="inlineStr">
@@ -45449,7 +45449,7 @@
       </c>
       <c r="H738" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I738" t="inlineStr">
@@ -45510,7 +45510,7 @@
       </c>
       <c r="H739" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I739" t="inlineStr">
@@ -45632,7 +45632,7 @@
       </c>
       <c r="H741" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I741" t="inlineStr">
@@ -45693,7 +45693,7 @@
       </c>
       <c r="H742" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I742" t="inlineStr">
@@ -45754,7 +45754,7 @@
       </c>
       <c r="H743" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I743" t="inlineStr">
@@ -45815,7 +45815,7 @@
       </c>
       <c r="H744" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I744" t="inlineStr">
@@ -45876,7 +45876,7 @@
       </c>
       <c r="H745" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I745" t="inlineStr">
@@ -45937,7 +45937,7 @@
       </c>
       <c r="H746" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I746" t="inlineStr">
@@ -45998,7 +45998,7 @@
       </c>
       <c r="H747" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I747" t="inlineStr">
@@ -46059,7 +46059,7 @@
       </c>
       <c r="H748" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I748" t="inlineStr">
@@ -46120,7 +46120,7 @@
       </c>
       <c r="H749" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I749" t="inlineStr">
@@ -46181,7 +46181,7 @@
       </c>
       <c r="H750" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I750" t="inlineStr">
@@ -46303,7 +46303,7 @@
       </c>
       <c r="H752" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I752" t="inlineStr">
@@ -46364,7 +46364,7 @@
       </c>
       <c r="H753" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I753" t="inlineStr">
@@ -46486,7 +46486,7 @@
       </c>
       <c r="H755" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I755" t="inlineStr">
@@ -46547,7 +46547,7 @@
       </c>
       <c r="H756" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I756" t="inlineStr">
@@ -46608,7 +46608,7 @@
       </c>
       <c r="H757" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I757" t="inlineStr">
@@ -46669,7 +46669,7 @@
       </c>
       <c r="H758" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I758" t="inlineStr">
@@ -46730,7 +46730,7 @@
       </c>
       <c r="H759" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I759" t="inlineStr">
@@ -46791,7 +46791,7 @@
       </c>
       <c r="H760" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I760" t="inlineStr">
@@ -46852,7 +46852,7 @@
       </c>
       <c r="H761" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I761" t="inlineStr">
@@ -46913,7 +46913,7 @@
       </c>
       <c r="H762" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I762" t="inlineStr">
@@ -46974,7 +46974,7 @@
       </c>
       <c r="H763" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I763" t="inlineStr">
@@ -47035,7 +47035,7 @@
       </c>
       <c r="H764" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I764" t="inlineStr">
@@ -47096,7 +47096,7 @@
       </c>
       <c r="H765" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I765" t="inlineStr">
@@ -47157,7 +47157,7 @@
       </c>
       <c r="H766" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I766" t="inlineStr">
@@ -47218,7 +47218,7 @@
       </c>
       <c r="H767" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I767" t="inlineStr">
@@ -47279,7 +47279,7 @@
       </c>
       <c r="H768" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I768" t="inlineStr">
@@ -47340,7 +47340,7 @@
       </c>
       <c r="H769" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I769" t="inlineStr">
@@ -47401,7 +47401,7 @@
       </c>
       <c r="H770" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I770" t="inlineStr">
@@ -47462,7 +47462,7 @@
       </c>
       <c r="H771" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I771" t="inlineStr">
@@ -47645,7 +47645,7 @@
       </c>
       <c r="H774" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I774" t="inlineStr">
@@ -47706,7 +47706,7 @@
       </c>
       <c r="H775" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I775" t="inlineStr">
@@ -47767,7 +47767,7 @@
       </c>
       <c r="H776" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I776" t="inlineStr">
@@ -47828,7 +47828,7 @@
       </c>
       <c r="H777" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I777" t="inlineStr">
@@ -47889,7 +47889,7 @@
       </c>
       <c r="H778" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I778" t="inlineStr">
@@ -47950,7 +47950,7 @@
       </c>
       <c r="H779" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I779" t="inlineStr">
@@ -48011,7 +48011,7 @@
       </c>
       <c r="H780" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I780" t="inlineStr">
@@ -48072,7 +48072,7 @@
       </c>
       <c r="H781" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I781" t="inlineStr">
@@ -48133,7 +48133,7 @@
       </c>
       <c r="H782" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I782" t="inlineStr">
@@ -48194,7 +48194,7 @@
       </c>
       <c r="H783" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I783" t="inlineStr">
@@ -48255,7 +48255,7 @@
       </c>
       <c r="H784" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I784" t="inlineStr">
@@ -48316,7 +48316,7 @@
       </c>
       <c r="H785" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I785" t="inlineStr">
@@ -48377,7 +48377,7 @@
       </c>
       <c r="H786" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I786" t="inlineStr">
@@ -48499,7 +48499,7 @@
       </c>
       <c r="H788" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I788" t="inlineStr">
@@ -48560,7 +48560,7 @@
       </c>
       <c r="H789" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I789" t="inlineStr">
@@ -48621,7 +48621,7 @@
       </c>
       <c r="H790" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I790" t="inlineStr">
@@ -48682,7 +48682,7 @@
       </c>
       <c r="H791" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I791" t="inlineStr">
@@ -48743,7 +48743,7 @@
       </c>
       <c r="H792" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I792" t="inlineStr">
@@ -48804,7 +48804,7 @@
       </c>
       <c r="H793" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I793" t="inlineStr">
@@ -48865,7 +48865,7 @@
       </c>
       <c r="H794" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I794" t="inlineStr">
@@ -48987,7 +48987,7 @@
       </c>
       <c r="H796" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I796" t="inlineStr">
@@ -49048,7 +49048,7 @@
       </c>
       <c r="H797" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I797" t="inlineStr">
@@ -49109,7 +49109,7 @@
       </c>
       <c r="H798" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I798" t="inlineStr">
@@ -49170,7 +49170,7 @@
       </c>
       <c r="H799" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I799" t="inlineStr">
@@ -49231,7 +49231,7 @@
       </c>
       <c r="H800" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I800" t="inlineStr">
@@ -49292,7 +49292,7 @@
       </c>
       <c r="H801" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I801" t="inlineStr">
@@ -49353,7 +49353,7 @@
       </c>
       <c r="H802" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I802" t="inlineStr">
@@ -49414,7 +49414,7 @@
       </c>
       <c r="H803" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I803" t="inlineStr">
@@ -49475,7 +49475,7 @@
       </c>
       <c r="H804" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I804" t="inlineStr">
@@ -49536,7 +49536,7 @@
       </c>
       <c r="H805" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I805" t="inlineStr">
@@ -49597,7 +49597,7 @@
       </c>
       <c r="H806" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I806" t="inlineStr">
@@ -49658,7 +49658,7 @@
       </c>
       <c r="H807" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I807" t="inlineStr">
@@ -49719,7 +49719,7 @@
       </c>
       <c r="H808" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I808" t="inlineStr">
@@ -49780,7 +49780,7 @@
       </c>
       <c r="H809" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I809" t="inlineStr">
@@ -49902,7 +49902,7 @@
       </c>
       <c r="H811" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I811" t="inlineStr">
@@ -49963,7 +49963,7 @@
       </c>
       <c r="H812" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I812" t="inlineStr">
@@ -50024,7 +50024,7 @@
       </c>
       <c r="H813" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I813" t="inlineStr">
@@ -50085,7 +50085,7 @@
       </c>
       <c r="H814" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I814" t="inlineStr">
@@ -50146,7 +50146,7 @@
       </c>
       <c r="H815" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I815" t="inlineStr">
@@ -50207,7 +50207,7 @@
       </c>
       <c r="H816" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I816" t="inlineStr">
@@ -50268,7 +50268,7 @@
       </c>
       <c r="H817" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I817" t="inlineStr">
@@ -50329,7 +50329,7 @@
       </c>
       <c r="H818" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I818" t="inlineStr">
@@ -50390,7 +50390,7 @@
       </c>
       <c r="H819" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I819" t="inlineStr">
@@ -50451,7 +50451,7 @@
       </c>
       <c r="H820" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I820" t="inlineStr">
@@ -50512,7 +50512,7 @@
       </c>
       <c r="H821" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I821" t="inlineStr">
@@ -50573,7 +50573,7 @@
       </c>
       <c r="H822" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I822" t="inlineStr">
@@ -50634,7 +50634,7 @@
       </c>
       <c r="H823" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I823" t="inlineStr">
@@ -50695,7 +50695,7 @@
       </c>
       <c r="H824" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I824" t="inlineStr">
@@ -50756,7 +50756,7 @@
       </c>
       <c r="H825" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I825" t="inlineStr">
@@ -50817,7 +50817,7 @@
       </c>
       <c r="H826" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I826" t="inlineStr">
@@ -50878,7 +50878,7 @@
       </c>
       <c r="H827" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I827" t="inlineStr">
@@ -50939,7 +50939,7 @@
       </c>
       <c r="H828" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I828" t="inlineStr">
@@ -51000,7 +51000,7 @@
       </c>
       <c r="H829" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I829" t="inlineStr">
@@ -51061,7 +51061,7 @@
       </c>
       <c r="H830" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I830" t="inlineStr">
@@ -51122,7 +51122,7 @@
       </c>
       <c r="H831" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I831" t="inlineStr">
@@ -51183,7 +51183,7 @@
       </c>
       <c r="H832" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I832" t="inlineStr">
@@ -51244,7 +51244,7 @@
       </c>
       <c r="H833" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I833" t="inlineStr">
@@ -51305,7 +51305,7 @@
       </c>
       <c r="H834" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I834" t="inlineStr">
@@ -51366,7 +51366,7 @@
       </c>
       <c r="H835" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I835" t="inlineStr">
@@ -51427,7 +51427,7 @@
       </c>
       <c r="H836" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I836" t="inlineStr">
@@ -51488,7 +51488,7 @@
       </c>
       <c r="H837" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I837" t="inlineStr">
@@ -51549,7 +51549,7 @@
       </c>
       <c r="H838" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I838" t="inlineStr">
@@ -51610,7 +51610,7 @@
       </c>
       <c r="H839" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I839" t="inlineStr">
@@ -51671,7 +51671,7 @@
       </c>
       <c r="H840" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I840" t="inlineStr">
@@ -51732,7 +51732,7 @@
       </c>
       <c r="H841" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I841" t="inlineStr">
@@ -51793,7 +51793,7 @@
       </c>
       <c r="H842" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I842" t="inlineStr">
@@ -51854,7 +51854,7 @@
       </c>
       <c r="H843" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I843" t="inlineStr">
@@ -51915,7 +51915,7 @@
       </c>
       <c r="H844" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I844" t="inlineStr">
@@ -51976,7 +51976,7 @@
       </c>
       <c r="H845" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I845" t="inlineStr">
@@ -52037,7 +52037,7 @@
       </c>
       <c r="H846" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I846" t="inlineStr">
@@ -52098,7 +52098,7 @@
       </c>
       <c r="H847" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I847" t="inlineStr">
@@ -52220,7 +52220,7 @@
       </c>
       <c r="H849" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I849" t="inlineStr">
@@ -52281,7 +52281,7 @@
       </c>
       <c r="H850" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I850" t="inlineStr">
@@ -52342,7 +52342,7 @@
       </c>
       <c r="H851" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I851" t="inlineStr">
@@ -52403,7 +52403,7 @@
       </c>
       <c r="H852" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I852" t="inlineStr">
@@ -52464,7 +52464,7 @@
       </c>
       <c r="H853" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I853" t="inlineStr">
@@ -52586,7 +52586,7 @@
       </c>
       <c r="H855" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I855" t="inlineStr">
@@ -52647,7 +52647,7 @@
       </c>
       <c r="H856" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I856" t="inlineStr">
@@ -52708,7 +52708,7 @@
       </c>
       <c r="H857" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I857" t="inlineStr">
@@ -52769,7 +52769,7 @@
       </c>
       <c r="H858" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I858" t="inlineStr">
@@ -52830,7 +52830,7 @@
       </c>
       <c r="H859" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I859" t="inlineStr">
@@ -52891,7 +52891,7 @@
       </c>
       <c r="H860" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I860" t="inlineStr">
@@ -53013,7 +53013,7 @@
       </c>
       <c r="H862" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I862" t="inlineStr">
@@ -53074,7 +53074,7 @@
       </c>
       <c r="H863" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I863" t="inlineStr">
@@ -53135,7 +53135,7 @@
       </c>
       <c r="H864" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I864" t="inlineStr">
@@ -53196,7 +53196,7 @@
       </c>
       <c r="H865" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I865" t="inlineStr">
@@ -53257,7 +53257,7 @@
       </c>
       <c r="H866" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I866" t="inlineStr">
@@ -53318,7 +53318,7 @@
       </c>
       <c r="H867" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I867" t="inlineStr">
@@ -53379,7 +53379,7 @@
       </c>
       <c r="H868" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I868" t="inlineStr">
@@ -53440,7 +53440,7 @@
       </c>
       <c r="H869" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I869" t="inlineStr">
@@ -53501,7 +53501,7 @@
       </c>
       <c r="H870" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I870" t="inlineStr">
@@ -53562,7 +53562,7 @@
       </c>
       <c r="H871" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I871" t="inlineStr">
@@ -53623,7 +53623,7 @@
       </c>
       <c r="H872" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I872" t="inlineStr">
@@ -53684,7 +53684,7 @@
       </c>
       <c r="H873" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I873" t="inlineStr">
@@ -53745,7 +53745,7 @@
       </c>
       <c r="H874" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I874" t="inlineStr">
@@ -53806,7 +53806,7 @@
       </c>
       <c r="H875" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I875" t="inlineStr">
@@ -53867,7 +53867,7 @@
       </c>
       <c r="H876" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I876" t="inlineStr">
@@ -53989,7 +53989,7 @@
       </c>
       <c r="H878" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I878" t="inlineStr">
@@ -54050,7 +54050,7 @@
       </c>
       <c r="H879" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I879" t="inlineStr">
@@ -54111,7 +54111,7 @@
       </c>
       <c r="H880" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I880" t="inlineStr">
@@ -54172,7 +54172,7 @@
       </c>
       <c r="H881" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I881" t="inlineStr">
@@ -54233,7 +54233,7 @@
       </c>
       <c r="H882" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I882" t="inlineStr">
@@ -54294,7 +54294,7 @@
       </c>
       <c r="H883" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I883" t="inlineStr">
@@ -54355,7 +54355,7 @@
       </c>
       <c r="H884" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I884" t="inlineStr">
@@ -54416,7 +54416,7 @@
       </c>
       <c r="H885" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I885" t="inlineStr">
@@ -54477,7 +54477,7 @@
       </c>
       <c r="H886" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I886" t="inlineStr">
@@ -54538,7 +54538,7 @@
       </c>
       <c r="H887" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I887" t="inlineStr">
@@ -54599,7 +54599,7 @@
       </c>
       <c r="H888" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I888" t="inlineStr">
@@ -54660,7 +54660,7 @@
       </c>
       <c r="H889" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I889" t="inlineStr">
@@ -54721,7 +54721,7 @@
       </c>
       <c r="H890" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I890" t="inlineStr">
@@ -54782,7 +54782,7 @@
       </c>
       <c r="H891" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I891" t="inlineStr">
@@ -54843,7 +54843,7 @@
       </c>
       <c r="H892" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I892" t="inlineStr">
@@ -54904,7 +54904,7 @@
       </c>
       <c r="H893" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I893" t="inlineStr">
@@ -54965,7 +54965,7 @@
       </c>
       <c r="H894" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I894" t="inlineStr">
@@ -55026,7 +55026,7 @@
       </c>
       <c r="H895" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I895" t="inlineStr">
@@ -55087,7 +55087,7 @@
       </c>
       <c r="H896" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I896" t="inlineStr">
@@ -55148,7 +55148,7 @@
       </c>
       <c r="H897" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I897" t="inlineStr">
@@ -55209,7 +55209,7 @@
       </c>
       <c r="H898" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I898" t="inlineStr">
@@ -55270,7 +55270,7 @@
       </c>
       <c r="H899" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I899" t="inlineStr">
@@ -55331,7 +55331,7 @@
       </c>
       <c r="H900" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I900" t="inlineStr">
@@ -55392,7 +55392,7 @@
       </c>
       <c r="H901" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I901" t="inlineStr">
@@ -55453,7 +55453,7 @@
       </c>
       <c r="H902" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I902" t="inlineStr">
@@ -55514,7 +55514,7 @@
       </c>
       <c r="H903" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I903" t="inlineStr">
@@ -55575,7 +55575,7 @@
       </c>
       <c r="H904" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I904" t="inlineStr">
@@ -55636,7 +55636,7 @@
       </c>
       <c r="H905" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I905" t="inlineStr">
@@ -55697,7 +55697,7 @@
       </c>
       <c r="H906" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I906" t="inlineStr">
@@ -55758,7 +55758,7 @@
       </c>
       <c r="H907" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I907" t="inlineStr">
@@ -55819,7 +55819,7 @@
       </c>
       <c r="H908" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I908" t="inlineStr">
@@ -55880,7 +55880,7 @@
       </c>
       <c r="H909" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I909" t="inlineStr">
@@ -55941,7 +55941,7 @@
       </c>
       <c r="H910" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I910" t="inlineStr">
@@ -56002,7 +56002,7 @@
       </c>
       <c r="H911" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I911" t="inlineStr">
@@ -56063,7 +56063,7 @@
       </c>
       <c r="H912" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I912" t="inlineStr">
@@ -56124,7 +56124,7 @@
       </c>
       <c r="H913" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I913" t="inlineStr">
@@ -56185,7 +56185,7 @@
       </c>
       <c r="H914" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I914" t="inlineStr">
@@ -56246,7 +56246,7 @@
       </c>
       <c r="H915" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I915" t="inlineStr">
@@ -56307,7 +56307,7 @@
       </c>
       <c r="H916" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I916" t="inlineStr">
@@ -56368,7 +56368,7 @@
       </c>
       <c r="H917" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I917" t="inlineStr">
@@ -56429,7 +56429,7 @@
       </c>
       <c r="H918" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I918" t="inlineStr">
@@ -56490,7 +56490,7 @@
       </c>
       <c r="H919" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I919" t="inlineStr">
@@ -56551,7 +56551,7 @@
       </c>
       <c r="H920" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I920" t="inlineStr">
@@ -56612,7 +56612,7 @@
       </c>
       <c r="H921" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I921" t="inlineStr">
@@ -56673,7 +56673,7 @@
       </c>
       <c r="H922" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I922" t="inlineStr">
@@ -56734,7 +56734,7 @@
       </c>
       <c r="H923" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I923" t="inlineStr">
@@ -56795,7 +56795,7 @@
       </c>
       <c r="H924" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I924" t="inlineStr">
@@ -56856,7 +56856,7 @@
       </c>
       <c r="H925" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I925" t="inlineStr">
@@ -56917,7 +56917,7 @@
       </c>
       <c r="H926" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I926" t="inlineStr">

--- a/docs/oc-mensuales/articulos-de-aseo-e-higiene/ago-2026.xlsx
+++ b/docs/oc-mensuales/articulos-de-aseo-e-higiene/ago-2026.xlsx
@@ -745,7 +745,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +871,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +936,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1001,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1066,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1131,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1257,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1383,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1448,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1513,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1578,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1643,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1769,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1834,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1899,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1964,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2029,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2094,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2159,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2224,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2289,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2354,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2785,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2850,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2915,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +2980,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3045,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3171,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3236,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3301,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3366,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3431,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3496,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3561,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3626,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3691,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3756,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3821,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3886,11 @@
           <t>78.209.441-6</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +3951,11 @@
           <t>77.823.479-3</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +4016,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3917,7 +4081,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4207,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4272,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4398,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4344,7 +4524,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4589,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4527,7 +4715,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4841,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +4967,11 @@
           <t>19.260.495-8</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +5093,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5015,7 +5219,11 @@
           <t>78.199.695-5</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5345,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5198,7 +5410,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5475,11 @@
           <t>79.722.860-5</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5320,7 +5540,11 @@
           <t>78.203.286-0</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5381,7 +5605,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5564,7 +5792,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5747,7 +5979,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5808,7 +6044,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5869,7 +6109,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5991,7 +6235,11 @@
           <t>77.404.653-4</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6052,7 +6300,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6113,7 +6365,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6174,7 +6430,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6235,7 +6495,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6296,7 +6560,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6357,7 +6625,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6418,7 +6690,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6479,7 +6755,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6540,7 +6820,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6601,7 +6885,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6662,7 +6950,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6723,7 +7015,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6906,7 +7202,11 @@
           <t>77.404.653-4</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6967,7 +7267,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7028,7 +7332,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7089,7 +7397,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7150,7 +7462,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7211,7 +7527,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7272,7 +7592,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7394,7 +7718,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7455,7 +7783,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7581,7 +7913,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7642,7 +7978,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7703,7 +8043,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7764,7 +8108,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7825,7 +8173,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7947,7 +8299,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8008,7 +8364,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8069,7 +8429,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8130,7 +8494,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8191,7 +8559,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8252,7 +8624,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8313,7 +8689,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8374,7 +8754,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8435,7 +8819,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8496,7 +8884,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8557,7 +8949,11 @@
           <t>78.076.237-3</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8618,7 +9014,11 @@
           <t>78.199.695-5</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8679,7 +9079,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8740,7 +9144,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8801,7 +9209,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8923,7 +9335,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8984,7 +9400,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9045,7 +9465,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9106,7 +9530,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9228,7 +9656,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9289,7 +9721,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9350,7 +9786,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9472,7 +9912,11 @@
           <t>78.209.481-5</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9533,7 +9977,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9594,7 +10042,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9655,7 +10107,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9716,7 +10172,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9777,7 +10237,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9838,7 +10302,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9899,7 +10367,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9960,7 +10432,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10143,7 +10619,11 @@
           <t>76.715.074-1</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10204,7 +10684,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10265,7 +10749,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10326,7 +10814,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10387,7 +10879,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10448,7 +10944,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10509,7 +11009,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10570,7 +11074,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10631,7 +11139,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10875,7 +11387,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10936,7 +11452,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10997,7 +11517,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11119,7 +11643,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11180,7 +11708,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11485,7 +12017,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11546,7 +12082,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11729,7 +12269,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11790,7 +12334,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11851,7 +12399,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11912,7 +12464,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12034,7 +12590,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12095,7 +12655,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12156,7 +12720,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12217,7 +12785,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12278,7 +12850,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12400,7 +12976,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12461,7 +13041,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12522,7 +13106,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12583,7 +13171,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12644,7 +13236,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12705,7 +13301,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12766,7 +13366,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12827,7 +13431,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12888,7 +13496,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12949,7 +13561,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13010,7 +13626,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13071,7 +13691,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13132,7 +13756,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13193,7 +13821,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13254,7 +13886,11 @@
           <t>77.720.988-4</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13315,7 +13951,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13376,7 +14016,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13437,7 +14081,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13559,7 +14207,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13620,7 +14272,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13742,7 +14398,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13803,7 +14463,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13864,7 +14528,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13925,7 +14593,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13986,7 +14658,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L222" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14047,7 +14723,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14169,7 +14849,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14230,7 +14914,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14291,7 +14979,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14352,7 +15044,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14413,7 +15109,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14474,7 +15174,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14535,7 +15239,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14596,7 +15304,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14657,7 +15369,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14718,7 +15434,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14779,7 +15499,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L235" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14840,7 +15564,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14962,7 +15690,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L238" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15023,7 +15755,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L239" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15084,7 +15820,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr"/>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L240" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15206,7 +15946,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr"/>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L242" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15328,7 +16072,11 @@
           <t>77.053.654-5</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr"/>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L244" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15450,7 +16198,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr"/>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L246" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15511,7 +16263,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr"/>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L247" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15572,7 +16328,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15755,7 +16515,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15877,7 +16641,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L253" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15938,7 +16706,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr"/>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L254" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16060,7 +16832,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr"/>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L256" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16304,7 +17080,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16365,7 +17145,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr"/>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L261" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16609,7 +17393,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr"/>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L265" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16853,7 +17641,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr"/>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16914,7 +17706,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr"/>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L270" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16975,7 +17771,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr"/>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L271" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17036,7 +17836,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr"/>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L272" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17097,7 +17901,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr"/>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L273" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17158,7 +17966,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr"/>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L274" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17219,7 +18031,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr"/>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L275" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17280,7 +18096,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K276" t="inlineStr"/>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L276" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17341,7 +18161,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K277" t="inlineStr"/>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L277" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17402,7 +18226,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K278" t="inlineStr"/>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L278" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17463,7 +18291,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr"/>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L279" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17524,7 +18356,11 @@
           <t>78.199.695-5</t>
         </is>
       </c>
-      <c r="K280" t="inlineStr"/>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L280" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17585,7 +18421,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr"/>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L281" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17646,7 +18486,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr"/>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L282" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17768,7 +18612,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K284" t="inlineStr"/>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L284" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17829,7 +18677,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr"/>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L285" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17890,7 +18742,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K286" t="inlineStr"/>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L286" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17951,7 +18807,11 @@
           <t>77.700.129-9</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr"/>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L287" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18012,7 +18872,11 @@
           <t>77.404.653-4</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr"/>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L288" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18134,7 +18998,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K290" t="inlineStr"/>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L290" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18195,7 +19063,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K291" t="inlineStr"/>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L291" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18256,7 +19128,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr"/>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L292" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18317,7 +19193,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K293" t="inlineStr"/>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L293" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18378,7 +19258,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K294" t="inlineStr"/>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L294" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18439,7 +19323,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K295" t="inlineStr"/>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L295" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18500,7 +19388,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr"/>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L296" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18561,7 +19453,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr"/>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L297" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18622,7 +19518,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K298" t="inlineStr"/>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L298" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18683,7 +19583,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K299" t="inlineStr"/>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L299" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18866,7 +19770,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K302" t="inlineStr"/>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L302" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18927,7 +19835,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K303" t="inlineStr"/>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L303" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18988,7 +19900,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K304" t="inlineStr"/>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L304" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19049,7 +19965,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K305" t="inlineStr"/>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L305" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19232,7 +20152,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K308" t="inlineStr"/>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L308" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19293,7 +20217,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr"/>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L309" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19354,7 +20282,11 @@
           <t>78.199.695-5</t>
         </is>
       </c>
-      <c r="K310" t="inlineStr"/>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L310" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19415,7 +20347,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr"/>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L311" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19476,7 +20412,11 @@
           <t>79.722.860-5</t>
         </is>
       </c>
-      <c r="K312" t="inlineStr"/>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L312" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19537,7 +20477,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K313" t="inlineStr"/>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L313" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19659,7 +20603,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K315" t="inlineStr"/>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L315" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19720,7 +20668,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K316" t="inlineStr"/>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L316" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19781,7 +20733,11 @@
           <t>96.989.530-7</t>
         </is>
       </c>
-      <c r="K317" t="inlineStr"/>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L317" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19903,7 +20859,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K319" t="inlineStr"/>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L319" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19964,7 +20924,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K320" t="inlineStr"/>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L320" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20025,7 +20989,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K321" t="inlineStr"/>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L321" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20086,7 +21054,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K322" t="inlineStr"/>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L322" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20208,7 +21180,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K324" t="inlineStr"/>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L324" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20391,7 +21367,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K327" t="inlineStr"/>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L327" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20513,7 +21493,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K329" t="inlineStr"/>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L329" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20635,7 +21619,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K331" t="inlineStr"/>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L331" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20818,7 +21806,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K334" t="inlineStr"/>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L334" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20940,7 +21932,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K336" t="inlineStr"/>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L336" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21123,7 +22119,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K339" t="inlineStr"/>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L339" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21245,7 +22245,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K341" t="inlineStr"/>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L341" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21428,7 +22432,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K344" t="inlineStr"/>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L344" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21489,7 +22497,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K345" t="inlineStr"/>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L345" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21550,7 +22562,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K346" t="inlineStr"/>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L346" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21611,7 +22627,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K347" t="inlineStr"/>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L347" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21794,7 +22814,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K350" t="inlineStr"/>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L350" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22099,7 +23123,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K355" t="inlineStr"/>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L355" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22221,7 +23249,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K357" t="inlineStr"/>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L357" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22282,7 +23314,11 @@
           <t>77.404.653-4</t>
         </is>
       </c>
-      <c r="K358" t="inlineStr"/>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L358" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22343,7 +23379,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K359" t="inlineStr"/>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L359" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22465,7 +23505,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K361" t="inlineStr"/>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L361" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22526,7 +23570,11 @@
           <t>77.404.653-4</t>
         </is>
       </c>
-      <c r="K362" t="inlineStr"/>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L362" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22587,7 +23635,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K363" t="inlineStr"/>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L363" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22648,7 +23700,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K364" t="inlineStr"/>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L364" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22709,7 +23765,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K365" t="inlineStr"/>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L365" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22770,7 +23830,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K366" t="inlineStr"/>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L366" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22831,7 +23895,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K367" t="inlineStr"/>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L367" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22892,7 +23960,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K368" t="inlineStr"/>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L368" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23014,7 +24086,11 @@
           <t>78.209.481-5</t>
         </is>
       </c>
-      <c r="K370" t="inlineStr"/>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L370" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23136,7 +24212,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K372" t="inlineStr"/>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L372" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23197,7 +24277,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K373" t="inlineStr"/>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L373" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23258,7 +24342,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K374" t="inlineStr"/>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L374" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23319,7 +24407,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K375" t="inlineStr"/>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L375" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23380,7 +24472,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K376" t="inlineStr"/>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L376" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23441,7 +24537,11 @@
           <t>78.199.695-5</t>
         </is>
       </c>
-      <c r="K377" t="inlineStr"/>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L377" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23502,7 +24602,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K378" t="inlineStr"/>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L378" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23563,7 +24667,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K379" t="inlineStr"/>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L379" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23685,7 +24793,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K381" t="inlineStr"/>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L381" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23807,7 +24919,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K383" t="inlineStr"/>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L383" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23868,7 +24984,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K384" t="inlineStr"/>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L384" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23929,7 +25049,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K385" t="inlineStr"/>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L385" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24051,7 +25175,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K387" t="inlineStr"/>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L387" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24112,7 +25240,11 @@
           <t>77.145.084-9</t>
         </is>
       </c>
-      <c r="K388" t="inlineStr"/>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L388" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24295,7 +25427,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K391" t="inlineStr"/>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L391" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24356,7 +25492,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K392" t="inlineStr"/>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L392" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24417,7 +25557,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K393" t="inlineStr"/>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L393" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24478,7 +25622,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K394" t="inlineStr"/>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L394" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24539,7 +25687,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K395" t="inlineStr"/>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L395" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24661,7 +25813,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K397" t="inlineStr"/>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L397" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24722,7 +25878,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K398" t="inlineStr"/>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L398" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24783,7 +25943,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K399" t="inlineStr"/>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L399" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24844,7 +26008,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K400" t="inlineStr"/>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L400" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24905,7 +26073,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K401" t="inlineStr"/>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L401" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24966,7 +26138,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K402" t="inlineStr"/>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L402" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25027,7 +26203,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K403" t="inlineStr"/>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L403" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25088,7 +26268,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K404" t="inlineStr"/>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L404" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25210,7 +26394,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K406" t="inlineStr"/>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L406" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25332,7 +26520,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K408" t="inlineStr"/>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L408" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25393,7 +26585,11 @@
           <t>77.346.435-9</t>
         </is>
       </c>
-      <c r="K409" t="inlineStr"/>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L409" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25454,7 +26650,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K410" t="inlineStr"/>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L410" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25515,7 +26715,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K411" t="inlineStr"/>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L411" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25576,7 +26780,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K412" t="inlineStr"/>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L412" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25637,7 +26845,11 @@
           <t>77.529.681-K</t>
         </is>
       </c>
-      <c r="K413" t="inlineStr"/>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L413" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25698,7 +26910,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K414" t="inlineStr"/>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L414" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25759,7 +26975,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K415" t="inlineStr"/>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L415" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25942,7 +27162,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K418" t="inlineStr"/>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L418" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26003,7 +27227,11 @@
           <t>77.547.396-7</t>
         </is>
       </c>
-      <c r="K419" t="inlineStr"/>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L419" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26064,7 +27292,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K420" t="inlineStr"/>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L420" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26125,7 +27357,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K421" t="inlineStr"/>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L421" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26186,7 +27422,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K422" t="inlineStr"/>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L422" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26247,7 +27487,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K423" t="inlineStr"/>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L423" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26430,7 +27674,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K426" t="inlineStr"/>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L426" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26491,7 +27739,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K427" t="inlineStr"/>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L427" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26674,7 +27926,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K430" t="inlineStr"/>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L430" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26735,7 +27991,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K431" t="inlineStr"/>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L431" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26857,7 +28117,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K433" t="inlineStr"/>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L433" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26918,7 +28182,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K434" t="inlineStr"/>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L434" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26979,7 +28247,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K435" t="inlineStr"/>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L435" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27101,7 +28373,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K437" t="inlineStr"/>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L437" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27284,7 +28560,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K440" t="inlineStr"/>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L440" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27406,7 +28686,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K442" t="inlineStr"/>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L442" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27528,7 +28812,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K444" t="inlineStr"/>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L444" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27589,7 +28877,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K445" t="inlineStr"/>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L445" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27711,7 +29003,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K447" t="inlineStr"/>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L447" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27833,7 +29129,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K449" t="inlineStr"/>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L449" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27955,7 +29255,11 @@
           <t>77.700.129-9</t>
         </is>
       </c>
-      <c r="K451" t="inlineStr"/>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L451" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28016,7 +29320,11 @@
           <t>77.935.401-6</t>
         </is>
       </c>
-      <c r="K452" t="inlineStr"/>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L452" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28077,7 +29385,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K453" t="inlineStr"/>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L453" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28138,7 +29450,11 @@
           <t>76.525.922-3</t>
         </is>
       </c>
-      <c r="K454" t="inlineStr"/>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L454" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28199,7 +29515,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K455" t="inlineStr"/>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L455" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28260,7 +29580,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K456" t="inlineStr"/>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L456" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28382,7 +29706,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K458" t="inlineStr"/>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L458" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28443,7 +29771,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K459" t="inlineStr"/>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L459" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28504,7 +29836,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K460" t="inlineStr"/>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L460" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28565,7 +29901,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K461" t="inlineStr"/>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L461" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28626,7 +29966,11 @@
           <t>78.199.695-5</t>
         </is>
       </c>
-      <c r="K462" t="inlineStr"/>
+      <c r="K462" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L462" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28687,7 +30031,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K463" t="inlineStr"/>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L463" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28748,7 +30096,11 @@
           <t>78.199.695-5</t>
         </is>
       </c>
-      <c r="K464" t="inlineStr"/>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L464" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28931,7 +30283,11 @@
           <t>76.100.933-8</t>
         </is>
       </c>
-      <c r="K467" t="inlineStr"/>
+      <c r="K467" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L467" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28992,7 +30348,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K468" t="inlineStr"/>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L468" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29053,7 +30413,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K469" t="inlineStr"/>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L469" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29236,7 +30600,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K472" t="inlineStr"/>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L472" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29358,7 +30726,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K474" t="inlineStr"/>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L474" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29480,7 +30852,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K476" t="inlineStr"/>
+      <c r="K476" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L476" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29541,7 +30917,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K477" t="inlineStr"/>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L477" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29602,7 +30982,11 @@
           <t>78.199.695-5</t>
         </is>
       </c>
-      <c r="K478" t="inlineStr"/>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L478" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29785,7 +31169,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K481" t="inlineStr"/>
+      <c r="K481" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L481" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29907,7 +31295,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K483" t="inlineStr"/>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L483" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29968,7 +31360,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K484" t="inlineStr"/>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L484" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30029,7 +31425,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K485" t="inlineStr"/>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L485" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30090,7 +31490,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K486" t="inlineStr"/>
+      <c r="K486" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L486" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30151,7 +31555,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K487" t="inlineStr"/>
+      <c r="K487" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L487" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30212,7 +31620,11 @@
           <t>77.505.828-5</t>
         </is>
       </c>
-      <c r="K488" t="inlineStr"/>
+      <c r="K488" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L488" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30334,7 +31746,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K490" t="inlineStr"/>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L490" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30456,7 +31872,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K492" t="inlineStr"/>
+      <c r="K492" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L492" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30578,7 +31998,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K494" t="inlineStr"/>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L494" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30639,7 +32063,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K495" t="inlineStr"/>
+      <c r="K495" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L495" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30761,7 +32189,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K497" t="inlineStr"/>
+      <c r="K497" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L497" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30822,7 +32254,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K498" t="inlineStr"/>
+      <c r="K498" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L498" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30944,7 +32380,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K500" t="inlineStr"/>
+      <c r="K500" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L500" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31005,7 +32445,11 @@
           <t>79.722.860-5</t>
         </is>
       </c>
-      <c r="K501" t="inlineStr"/>
+      <c r="K501" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L501" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31066,7 +32510,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K502" t="inlineStr"/>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L502" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31127,7 +32575,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K503" t="inlineStr"/>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L503" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31432,7 +32884,11 @@
           <t>78.209.499-8</t>
         </is>
       </c>
-      <c r="K508" t="inlineStr"/>
+      <c r="K508" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L508" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31554,7 +33010,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K510" t="inlineStr"/>
+      <c r="K510" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L510" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31676,7 +33136,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K512" t="inlineStr"/>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L512" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31737,7 +33201,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K513" t="inlineStr"/>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L513" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31798,7 +33266,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K514" t="inlineStr"/>
+      <c r="K514" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L514" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31920,7 +33392,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K516" t="inlineStr"/>
+      <c r="K516" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L516" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31981,7 +33457,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K517" t="inlineStr"/>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L517" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32103,7 +33583,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K519" t="inlineStr"/>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L519" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32164,7 +33648,11 @@
           <t>78.203.286-0</t>
         </is>
       </c>
-      <c r="K520" t="inlineStr"/>
+      <c r="K520" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L520" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32225,7 +33713,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K521" t="inlineStr"/>
+      <c r="K521" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L521" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32286,7 +33778,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K522" t="inlineStr"/>
+      <c r="K522" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L522" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32347,7 +33843,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K523" t="inlineStr"/>
+      <c r="K523" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L523" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32408,7 +33908,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K524" t="inlineStr"/>
+      <c r="K524" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L524" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32469,7 +33973,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K525" t="inlineStr"/>
+      <c r="K525" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L525" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32530,7 +34038,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K526" t="inlineStr"/>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L526" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32652,7 +34164,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K528" t="inlineStr"/>
+      <c r="K528" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L528" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32835,7 +34351,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K531" t="inlineStr"/>
+      <c r="K531" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L531" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32957,7 +34477,11 @@
           <t>77.700.129-9</t>
         </is>
       </c>
-      <c r="K533" t="inlineStr"/>
+      <c r="K533" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L533" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33018,7 +34542,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K534" t="inlineStr"/>
+      <c r="K534" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L534" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33079,7 +34607,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K535" t="inlineStr"/>
+      <c r="K535" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L535" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33140,7 +34672,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K536" t="inlineStr"/>
+      <c r="K536" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L536" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33201,7 +34737,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K537" t="inlineStr"/>
+      <c r="K537" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L537" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33262,7 +34802,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K538" t="inlineStr"/>
+      <c r="K538" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L538" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33445,7 +34989,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K541" t="inlineStr"/>
+      <c r="K541" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L541" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33506,7 +35054,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K542" t="inlineStr"/>
+      <c r="K542" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L542" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33750,7 +35302,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K546" t="inlineStr"/>
+      <c r="K546" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L546" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33811,7 +35367,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K547" t="inlineStr"/>
+      <c r="K547" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L547" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33933,7 +35493,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K549" t="inlineStr"/>
+      <c r="K549" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L549" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33994,7 +35558,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K550" t="inlineStr"/>
+      <c r="K550" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L550" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34116,7 +35684,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K552" t="inlineStr"/>
+      <c r="K552" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L552" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34177,7 +35749,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K553" t="inlineStr"/>
+      <c r="K553" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L553" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34299,7 +35875,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K555" t="inlineStr"/>
+      <c r="K555" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L555" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34421,7 +36001,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K557" t="inlineStr"/>
+      <c r="K557" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L557" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34604,7 +36188,11 @@
           <t>79.722.860-5</t>
         </is>
       </c>
-      <c r="K560" t="inlineStr"/>
+      <c r="K560" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L560" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34665,7 +36253,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K561" t="inlineStr"/>
+      <c r="K561" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L561" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34726,7 +36318,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K562" t="inlineStr"/>
+      <c r="K562" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L562" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34787,7 +36383,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K563" t="inlineStr"/>
+      <c r="K563" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L563" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34848,7 +36448,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K564" t="inlineStr"/>
+      <c r="K564" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L564" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35031,7 +36635,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K567" t="inlineStr"/>
+      <c r="K567" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L567" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35092,7 +36700,11 @@
           <t>77.720.988-4</t>
         </is>
       </c>
-      <c r="K568" t="inlineStr"/>
+      <c r="K568" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L568" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35153,7 +36765,11 @@
           <t>19.260.495-8</t>
         </is>
       </c>
-      <c r="K569" t="inlineStr"/>
+      <c r="K569" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L569" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35214,7 +36830,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K570" t="inlineStr"/>
+      <c r="K570" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L570" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35275,7 +36895,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K571" t="inlineStr"/>
+      <c r="K571" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L571" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35397,7 +37021,11 @@
           <t>77.619.564-2</t>
         </is>
       </c>
-      <c r="K573" t="inlineStr"/>
+      <c r="K573" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L573" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35458,7 +37086,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K574" t="inlineStr"/>
+      <c r="K574" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L574" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35580,7 +37212,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K576" t="inlineStr"/>
+      <c r="K576" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L576" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35641,7 +37277,11 @@
           <t>78.212.867-1</t>
         </is>
       </c>
-      <c r="K577" t="inlineStr"/>
+      <c r="K577" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L577" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35763,7 +37403,11 @@
           <t>77.454.264-7</t>
         </is>
       </c>
-      <c r="K579" t="inlineStr"/>
+      <c r="K579" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L579" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35824,7 +37468,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K580" t="inlineStr"/>
+      <c r="K580" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L580" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35946,7 +37594,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K582" t="inlineStr"/>
+      <c r="K582" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L582" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36007,7 +37659,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K583" t="inlineStr"/>
+      <c r="K583" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L583" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36068,7 +37724,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K584" t="inlineStr"/>
+      <c r="K584" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L584" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36129,7 +37789,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K585" t="inlineStr"/>
+      <c r="K585" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L585" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36190,7 +37854,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K586" t="inlineStr"/>
+      <c r="K586" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L586" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36312,7 +37980,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K588" t="inlineStr"/>
+      <c r="K588" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L588" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36373,7 +38045,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K589" t="inlineStr"/>
+      <c r="K589" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L589" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36434,7 +38110,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K590" t="inlineStr"/>
+      <c r="K590" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L590" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36495,7 +38175,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K591" t="inlineStr"/>
+      <c r="K591" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L591" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36678,7 +38362,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K594" t="inlineStr"/>
+      <c r="K594" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L594" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36739,7 +38427,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K595" t="inlineStr"/>
+      <c r="K595" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L595" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36800,7 +38492,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K596" t="inlineStr"/>
+      <c r="K596" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L596" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36861,7 +38557,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K597" t="inlineStr"/>
+      <c r="K597" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L597" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36922,7 +38622,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K598" t="inlineStr"/>
+      <c r="K598" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L598" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36983,7 +38687,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K599" t="inlineStr"/>
+      <c r="K599" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L599" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37105,7 +38813,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K601" t="inlineStr"/>
+      <c r="K601" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L601" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37166,7 +38878,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K602" t="inlineStr"/>
+      <c r="K602" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L602" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37227,7 +38943,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K603" t="inlineStr"/>
+      <c r="K603" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L603" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37349,7 +39069,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K605" t="inlineStr"/>
+      <c r="K605" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L605" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37410,7 +39134,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K606" t="inlineStr"/>
+      <c r="K606" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L606" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37532,7 +39260,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K608" t="inlineStr"/>
+      <c r="K608" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L608" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37654,7 +39386,11 @@
           <t>77.404.653-4</t>
         </is>
       </c>
-      <c r="K610" t="inlineStr"/>
+      <c r="K610" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L610" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37837,7 +39573,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K613" t="inlineStr"/>
+      <c r="K613" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L613" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37959,7 +39699,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K615" t="inlineStr"/>
+      <c r="K615" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L615" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38020,7 +39764,11 @@
           <t>78.199.695-5</t>
         </is>
       </c>
-      <c r="K616" t="inlineStr"/>
+      <c r="K616" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L616" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38081,7 +39829,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K617" t="inlineStr"/>
+      <c r="K617" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L617" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38142,7 +39894,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K618" t="inlineStr"/>
+      <c r="K618" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L618" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38203,7 +39959,11 @@
           <t>77.884.798-1</t>
         </is>
       </c>
-      <c r="K619" t="inlineStr"/>
+      <c r="K619" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L619" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38264,7 +40024,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K620" t="inlineStr"/>
+      <c r="K620" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L620" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38325,7 +40089,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K621" t="inlineStr"/>
+      <c r="K621" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L621" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38386,7 +40154,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K622" t="inlineStr"/>
+      <c r="K622" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L622" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38508,7 +40280,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K624" t="inlineStr"/>
+      <c r="K624" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L624" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38569,7 +40345,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K625" t="inlineStr"/>
+      <c r="K625" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L625" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38630,7 +40410,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K626" t="inlineStr"/>
+      <c r="K626" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L626" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38691,7 +40475,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K627" t="inlineStr"/>
+      <c r="K627" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L627" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38752,7 +40540,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K628" t="inlineStr"/>
+      <c r="K628" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L628" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38813,7 +40605,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K629" t="inlineStr"/>
+      <c r="K629" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L629" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38874,7 +40670,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K630" t="inlineStr"/>
+      <c r="K630" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L630" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38935,7 +40735,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K631" t="inlineStr"/>
+      <c r="K631" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L631" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38996,7 +40800,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K632" t="inlineStr"/>
+      <c r="K632" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L632" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39057,7 +40865,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K633" t="inlineStr"/>
+      <c r="K633" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L633" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39118,7 +40930,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K634" t="inlineStr"/>
+      <c r="K634" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L634" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39423,7 +41239,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K639" t="inlineStr"/>
+      <c r="K639" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L639" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39484,7 +41304,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K640" t="inlineStr"/>
+      <c r="K640" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L640" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39545,7 +41369,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K641" t="inlineStr"/>
+      <c r="K641" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L641" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39606,7 +41434,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K642" t="inlineStr"/>
+      <c r="K642" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L642" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39728,7 +41560,11 @@
           <t>77.623.039-1</t>
         </is>
       </c>
-      <c r="K644" t="inlineStr"/>
+      <c r="K644" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L644" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39789,7 +41625,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K645" t="inlineStr"/>
+      <c r="K645" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L645" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39911,7 +41751,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K647" t="inlineStr"/>
+      <c r="K647" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L647" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39972,7 +41816,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K648" t="inlineStr"/>
+      <c r="K648" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L648" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40033,7 +41881,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K649" t="inlineStr"/>
+      <c r="K649" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L649" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40094,7 +41946,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K650" t="inlineStr"/>
+      <c r="K650" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L650" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40155,7 +42011,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K651" t="inlineStr"/>
+      <c r="K651" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L651" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40216,7 +42076,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K652" t="inlineStr"/>
+      <c r="K652" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L652" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40338,7 +42202,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K654" t="inlineStr"/>
+      <c r="K654" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L654" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40521,7 +42389,11 @@
           <t>77.745.829-9</t>
         </is>
       </c>
-      <c r="K657" t="inlineStr"/>
+      <c r="K657" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L657" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40643,7 +42515,11 @@
           <t>78.209.499-8</t>
         </is>
       </c>
-      <c r="K659" t="inlineStr"/>
+      <c r="K659" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L659" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40704,7 +42580,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K660" t="inlineStr"/>
+      <c r="K660" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L660" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40826,7 +42706,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K662" t="inlineStr"/>
+      <c r="K662" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L662" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40887,7 +42771,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K663" t="inlineStr"/>
+      <c r="K663" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L663" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40948,7 +42836,11 @@
           <t>78.203.286-0</t>
         </is>
       </c>
-      <c r="K664" t="inlineStr"/>
+      <c r="K664" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L664" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41009,7 +42901,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K665" t="inlineStr"/>
+      <c r="K665" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L665" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41070,7 +42966,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K666" t="inlineStr"/>
+      <c r="K666" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L666" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41131,7 +43031,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K667" t="inlineStr"/>
+      <c r="K667" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L667" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41192,7 +43096,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K668" t="inlineStr"/>
+      <c r="K668" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L668" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41253,7 +43161,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K669" t="inlineStr"/>
+      <c r="K669" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L669" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41375,7 +43287,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K671" t="inlineStr"/>
+      <c r="K671" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L671" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41497,7 +43413,11 @@
           <t>77.621.112-5</t>
         </is>
       </c>
-      <c r="K673" t="inlineStr"/>
+      <c r="K673" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L673" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41558,7 +43478,11 @@
           <t>77.404.653-4</t>
         </is>
       </c>
-      <c r="K674" t="inlineStr"/>
+      <c r="K674" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L674" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41680,7 +43604,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K676" t="inlineStr"/>
+      <c r="K676" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L676" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41741,7 +43669,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K677" t="inlineStr"/>
+      <c r="K677" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L677" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41802,7 +43734,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K678" t="inlineStr"/>
+      <c r="K678" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L678" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41985,7 +43921,11 @@
           <t>78.209.499-8</t>
         </is>
       </c>
-      <c r="K681" t="inlineStr"/>
+      <c r="K681" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L681" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42107,7 +44047,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K683" t="inlineStr"/>
+      <c r="K683" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L683" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42168,7 +44112,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K684" t="inlineStr"/>
+      <c r="K684" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L684" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42229,7 +44177,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K685" t="inlineStr"/>
+      <c r="K685" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L685" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42290,7 +44242,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K686" t="inlineStr"/>
+      <c r="K686" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L686" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42351,7 +44307,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K687" t="inlineStr"/>
+      <c r="K687" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L687" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42412,7 +44372,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K688" t="inlineStr"/>
+      <c r="K688" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L688" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42473,7 +44437,11 @@
           <t>77.700.129-9</t>
         </is>
       </c>
-      <c r="K689" t="inlineStr"/>
+      <c r="K689" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L689" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42534,7 +44502,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K690" t="inlineStr"/>
+      <c r="K690" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L690" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42595,7 +44567,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K691" t="inlineStr"/>
+      <c r="K691" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L691" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42656,7 +44632,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K692" t="inlineStr"/>
+      <c r="K692" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L692" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42717,7 +44697,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K693" t="inlineStr"/>
+      <c r="K693" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L693" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42778,7 +44762,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K694" t="inlineStr"/>
+      <c r="K694" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L694" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42839,7 +44827,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K695" t="inlineStr"/>
+      <c r="K695" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L695" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42900,7 +44892,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K696" t="inlineStr"/>
+      <c r="K696" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L696" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43022,7 +45018,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K698" t="inlineStr"/>
+      <c r="K698" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L698" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43144,7 +45144,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K700" t="inlineStr"/>
+      <c r="K700" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L700" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43205,7 +45209,11 @@
           <t>77.649.678-2</t>
         </is>
       </c>
-      <c r="K701" t="inlineStr"/>
+      <c r="K701" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L701" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43327,7 +45335,11 @@
           <t>77.806.000-0</t>
         </is>
       </c>
-      <c r="K703" t="inlineStr"/>
+      <c r="K703" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L703" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43388,7 +45400,11 @@
           <t>77.700.129-9</t>
         </is>
       </c>
-      <c r="K704" t="inlineStr"/>
+      <c r="K704" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L704" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43510,7 +45526,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K706" t="inlineStr"/>
+      <c r="K706" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L706" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43571,7 +45591,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K707" t="inlineStr"/>
+      <c r="K707" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L707" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43632,7 +45656,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K708" t="inlineStr"/>
+      <c r="K708" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L708" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43754,7 +45782,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K710" t="inlineStr"/>
+      <c r="K710" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L710" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43815,7 +45847,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K711" t="inlineStr"/>
+      <c r="K711" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L711" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43876,7 +45912,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K712" t="inlineStr"/>
+      <c r="K712" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L712" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43937,7 +45977,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K713" t="inlineStr"/>
+      <c r="K713" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L713" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43998,7 +46042,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K714" t="inlineStr"/>
+      <c r="K714" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L714" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44059,7 +46107,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K715" t="inlineStr"/>
+      <c r="K715" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L715" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44181,7 +46233,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K717" t="inlineStr"/>
+      <c r="K717" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L717" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44242,7 +46298,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K718" t="inlineStr"/>
+      <c r="K718" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L718" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44303,7 +46363,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K719" t="inlineStr"/>
+      <c r="K719" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L719" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44364,7 +46428,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K720" t="inlineStr"/>
+      <c r="K720" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L720" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44425,7 +46493,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K721" t="inlineStr"/>
+      <c r="K721" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L721" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44486,7 +46558,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K722" t="inlineStr"/>
+      <c r="K722" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L722" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44730,7 +46806,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K726" t="inlineStr"/>
+      <c r="K726" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L726" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44791,7 +46871,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K727" t="inlineStr"/>
+      <c r="K727" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L727" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44852,7 +46936,11 @@
           <t>77.406.941-0</t>
         </is>
       </c>
-      <c r="K728" t="inlineStr"/>
+      <c r="K728" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L728" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44913,7 +47001,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K729" t="inlineStr"/>
+      <c r="K729" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L729" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45218,7 +47310,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K734" t="inlineStr"/>
+      <c r="K734" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L734" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45401,7 +47497,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K737" t="inlineStr"/>
+      <c r="K737" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L737" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45462,7 +47562,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K738" t="inlineStr"/>
+      <c r="K738" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L738" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45523,7 +47627,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K739" t="inlineStr"/>
+      <c r="K739" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L739" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45584,7 +47692,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K740" t="inlineStr"/>
+      <c r="K740" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L740" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45645,7 +47757,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K741" t="inlineStr"/>
+      <c r="K741" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L741" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45706,7 +47822,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K742" t="inlineStr"/>
+      <c r="K742" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L742" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45767,7 +47887,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K743" t="inlineStr"/>
+      <c r="K743" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L743" t="inlineStr">
         <is>
           <t>USD</t>
@@ -45889,7 +48013,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K745" t="inlineStr"/>
+      <c r="K745" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L745" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46011,7 +48139,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K747" t="inlineStr"/>
+      <c r="K747" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L747" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46133,7 +48265,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K749" t="inlineStr"/>
+      <c r="K749" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L749" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46194,7 +48330,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K750" t="inlineStr"/>
+      <c r="K750" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L750" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46316,7 +48456,11 @@
           <t>78.209.499-8</t>
         </is>
       </c>
-      <c r="K752" t="inlineStr"/>
+      <c r="K752" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L752" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46377,7 +48521,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K753" t="inlineStr"/>
+      <c r="K753" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L753" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46438,7 +48586,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K754" t="inlineStr"/>
+      <c r="K754" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L754" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46499,7 +48651,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K755" t="inlineStr"/>
+      <c r="K755" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L755" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46560,7 +48716,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K756" t="inlineStr"/>
+      <c r="K756" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L756" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46621,7 +48781,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K757" t="inlineStr"/>
+      <c r="K757" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L757" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46804,7 +48968,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K760" t="inlineStr"/>
+      <c r="K760" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L760" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46865,7 +49033,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K761" t="inlineStr"/>
+      <c r="K761" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L761" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46987,7 +49159,11 @@
           <t>77.700.129-9</t>
         </is>
       </c>
-      <c r="K763" t="inlineStr"/>
+      <c r="K763" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L763" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47109,7 +49285,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K765" t="inlineStr"/>
+      <c r="K765" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L765" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47231,7 +49411,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K767" t="inlineStr"/>
+      <c r="K767" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L767" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47292,7 +49476,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K768" t="inlineStr"/>
+      <c r="K768" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L768" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47353,7 +49541,11 @@
           <t>77.404.653-4</t>
         </is>
       </c>
-      <c r="K769" t="inlineStr"/>
+      <c r="K769" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L769" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47414,7 +49606,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K770" t="inlineStr"/>
+      <c r="K770" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L770" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47475,7 +49671,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K771" t="inlineStr"/>
+      <c r="K771" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L771" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47536,7 +49736,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K772" t="inlineStr"/>
+      <c r="K772" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L772" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47597,7 +49801,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K773" t="inlineStr"/>
+      <c r="K773" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L773" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47658,7 +49866,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K774" t="inlineStr"/>
+      <c r="K774" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L774" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47719,7 +49931,11 @@
           <t>77.404.653-4</t>
         </is>
       </c>
-      <c r="K775" t="inlineStr"/>
+      <c r="K775" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L775" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47780,7 +49996,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K776" t="inlineStr"/>
+      <c r="K776" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L776" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47902,7 +50122,11 @@
           <t>78.212.867-1</t>
         </is>
       </c>
-      <c r="K778" t="inlineStr"/>
+      <c r="K778" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L778" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47963,7 +50187,11 @@
           <t>77.020.146-2</t>
         </is>
       </c>
-      <c r="K779" t="inlineStr"/>
+      <c r="K779" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L779" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48085,7 +50313,11 @@
           <t>77.082.051-0</t>
         </is>
       </c>
-      <c r="K781" t="inlineStr"/>
+      <c r="K781" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L781" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48329,7 +50561,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K785" t="inlineStr"/>
+      <c r="K785" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L785" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48390,7 +50626,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K786" t="inlineStr"/>
+      <c r="K786" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L786" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48756,7 +50996,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K792" t="inlineStr"/>
+      <c r="K792" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L792" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48817,7 +51061,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K793" t="inlineStr"/>
+      <c r="K793" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L793" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48878,7 +51126,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K794" t="inlineStr"/>
+      <c r="K794" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L794" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49000,7 +51252,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K796" t="inlineStr"/>
+      <c r="K796" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L796" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49061,7 +51317,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K797" t="inlineStr"/>
+      <c r="K797" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L797" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49183,7 +51443,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K799" t="inlineStr"/>
+      <c r="K799" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L799" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49244,7 +51508,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K800" t="inlineStr"/>
+      <c r="K800" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L800" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49305,7 +51573,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K801" t="inlineStr"/>
+      <c r="K801" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L801" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49366,7 +51638,11 @@
           <t>77.328.681-7</t>
         </is>
       </c>
-      <c r="K802" t="inlineStr"/>
+      <c r="K802" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L802" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49427,7 +51703,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K803" t="inlineStr"/>
+      <c r="K803" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L803" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49488,7 +51768,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K804" t="inlineStr"/>
+      <c r="K804" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L804" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49549,7 +51833,11 @@
           <t>77.404.653-4</t>
         </is>
       </c>
-      <c r="K805" t="inlineStr"/>
+      <c r="K805" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L805" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49610,7 +51898,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K806" t="inlineStr"/>
+      <c r="K806" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L806" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49793,7 +52085,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K809" t="inlineStr"/>
+      <c r="K809" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L809" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49854,7 +52150,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K810" t="inlineStr"/>
+      <c r="K810" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L810" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49915,7 +52215,11 @@
           <t>77.725.256-9</t>
         </is>
       </c>
-      <c r="K811" t="inlineStr"/>
+      <c r="K811" t="inlineStr">
+        <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
       <c r="L811" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50098,7 +52402,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K814" t="inlineStr"/>
+      <c r="K814" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L814" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50281,7 +52589,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K817" t="inlineStr"/>
+      <c r="K817" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L817" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50342,7 +52654,11 @@
           <t>77.404.653-4</t>
         </is>
       </c>
-      <c r="K818" t="inlineStr"/>
+      <c r="K818" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L818" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50647,7 +52963,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K823" t="inlineStr"/>
+      <c r="K823" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L823" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50708,7 +53028,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K824" t="inlineStr"/>
+      <c r="K824" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L824" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50769,7 +53093,11 @@
           <t>78.212.867-1</t>
         </is>
       </c>
-      <c r="K825" t="inlineStr"/>
+      <c r="K825" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L825" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50830,7 +53158,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K826" t="inlineStr"/>
+      <c r="K826" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L826" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50891,7 +53223,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K827" t="inlineStr"/>
+      <c r="K827" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L827" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50952,7 +53288,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K828" t="inlineStr"/>
+      <c r="K828" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L828" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51013,7 +53353,11 @@
           <t>78.199.695-5</t>
         </is>
       </c>
-      <c r="K829" t="inlineStr"/>
+      <c r="K829" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L829" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51135,7 +53479,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K831" t="inlineStr"/>
+      <c r="K831" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L831" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51196,7 +53544,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K832" t="inlineStr"/>
+      <c r="K832" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L832" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51257,7 +53609,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K833" t="inlineStr"/>
+      <c r="K833" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L833" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51318,7 +53674,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K834" t="inlineStr"/>
+      <c r="K834" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L834" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51440,7 +53800,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K836" t="inlineStr"/>
+      <c r="K836" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L836" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51501,7 +53865,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K837" t="inlineStr"/>
+      <c r="K837" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L837" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51562,7 +53930,11 @@
           <t>78.199.695-5</t>
         </is>
       </c>
-      <c r="K838" t="inlineStr"/>
+      <c r="K838" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L838" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51623,7 +53995,11 @@
           <t>78.061.716-0</t>
         </is>
       </c>
-      <c r="K839" t="inlineStr"/>
+      <c r="K839" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L839" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51684,7 +54060,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K840" t="inlineStr"/>
+      <c r="K840" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L840" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51806,7 +54186,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K842" t="inlineStr"/>
+      <c r="K842" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L842" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51867,7 +54251,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K843" t="inlineStr"/>
+      <c r="K843" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L843" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51928,7 +54316,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K844" t="inlineStr"/>
+      <c r="K844" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L844" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52111,7 +54503,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K847" t="inlineStr"/>
+      <c r="K847" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L847" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52172,7 +54568,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K848" t="inlineStr"/>
+      <c r="K848" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L848" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52233,7 +54633,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K849" t="inlineStr"/>
+      <c r="K849" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L849" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52355,7 +54759,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K851" t="inlineStr"/>
+      <c r="K851" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L851" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52477,7 +54885,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K853" t="inlineStr"/>
+      <c r="K853" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L853" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52538,7 +54950,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K854" t="inlineStr"/>
+      <c r="K854" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L854" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52599,7 +55015,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K855" t="inlineStr"/>
+      <c r="K855" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L855" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52660,7 +55080,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K856" t="inlineStr"/>
+      <c r="K856" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L856" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52721,7 +55145,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K857" t="inlineStr"/>
+      <c r="K857" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L857" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52843,7 +55271,11 @@
           <t>76.202.065-3</t>
         </is>
       </c>
-      <c r="K859" t="inlineStr"/>
+      <c r="K859" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L859" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52904,7 +55336,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K860" t="inlineStr"/>
+      <c r="K860" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L860" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52965,7 +55401,11 @@
           <t>77.404.653-4</t>
         </is>
       </c>
-      <c r="K861" t="inlineStr"/>
+      <c r="K861" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L861" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53026,7 +55466,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K862" t="inlineStr"/>
+      <c r="K862" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L862" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53270,7 +55714,11 @@
           <t>77.610.393-4</t>
         </is>
       </c>
-      <c r="K866" t="inlineStr"/>
+      <c r="K866" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L866" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53331,7 +55779,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K867" t="inlineStr"/>
+      <c r="K867" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L867" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53392,7 +55844,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K868" t="inlineStr"/>
+      <c r="K868" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L868" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53453,7 +55909,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K869" t="inlineStr"/>
+      <c r="K869" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L869" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53514,7 +55974,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K870" t="inlineStr"/>
+      <c r="K870" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L870" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53575,7 +56039,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K871" t="inlineStr"/>
+      <c r="K871" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L871" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53636,7 +56104,11 @@
           <t>77.935.401-6</t>
         </is>
       </c>
-      <c r="K872" t="inlineStr"/>
+      <c r="K872" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L872" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53697,7 +56169,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K873" t="inlineStr"/>
+      <c r="K873" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L873" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53941,7 +56417,11 @@
           <t>78.307.990-9</t>
         </is>
       </c>
-      <c r="K877" t="inlineStr"/>
+      <c r="K877" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L877" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54063,7 +56543,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K879" t="inlineStr"/>
+      <c r="K879" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L879" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54185,7 +56669,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K881" t="inlineStr"/>
+      <c r="K881" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L881" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54246,7 +56734,11 @@
           <t>77.537.871-9</t>
         </is>
       </c>
-      <c r="K882" t="inlineStr"/>
+      <c r="K882" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L882" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54307,7 +56799,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K883" t="inlineStr"/>
+      <c r="K883" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L883" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54368,7 +56864,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K884" t="inlineStr"/>
+      <c r="K884" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L884" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54429,7 +56929,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K885" t="inlineStr"/>
+      <c r="K885" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L885" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54490,7 +56994,11 @@
           <t>77.404.653-4</t>
         </is>
       </c>
-      <c r="K886" t="inlineStr"/>
+      <c r="K886" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L886" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54551,7 +57059,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K887" t="inlineStr"/>
+      <c r="K887" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L887" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54734,7 +57246,11 @@
           <t>76.540.457-6</t>
         </is>
       </c>
-      <c r="K890" t="inlineStr"/>
+      <c r="K890" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L890" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54795,7 +57311,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K891" t="inlineStr"/>
+      <c r="K891" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L891" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54856,7 +57376,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K892" t="inlineStr"/>
+      <c r="K892" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L892" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54978,7 +57502,11 @@
           <t>78.188.383-2</t>
         </is>
       </c>
-      <c r="K894" t="inlineStr"/>
+      <c r="K894" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L894" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55100,7 +57628,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K896" t="inlineStr"/>
+      <c r="K896" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L896" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55161,7 +57693,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K897" t="inlineStr"/>
+      <c r="K897" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L897" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55222,7 +57758,11 @@
           <t>76.100.732-7</t>
         </is>
       </c>
-      <c r="K898" t="inlineStr"/>
+      <c r="K898" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L898" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55283,7 +57823,11 @@
           <t>77.012.870-6</t>
         </is>
       </c>
-      <c r="K899" t="inlineStr"/>
+      <c r="K899" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L899" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55344,7 +57888,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K900" t="inlineStr"/>
+      <c r="K900" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L900" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55527,7 +58075,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K903" t="inlineStr"/>
+      <c r="K903" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L903" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55588,7 +58140,11 @@
           <t>76.710.414-6</t>
         </is>
       </c>
-      <c r="K904" t="inlineStr"/>
+      <c r="K904" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L904" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55710,7 +58266,11 @@
           <t>77.404.653-4</t>
         </is>
       </c>
-      <c r="K906" t="inlineStr"/>
+      <c r="K906" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L906" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55771,7 +58331,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K907" t="inlineStr"/>
+      <c r="K907" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L907" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55893,7 +58457,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K909" t="inlineStr"/>
+      <c r="K909" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L909" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56015,7 +58583,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K911" t="inlineStr"/>
+      <c r="K911" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L911" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56076,7 +58648,11 @@
           <t>78.906.980-8</t>
         </is>
       </c>
-      <c r="K912" t="inlineStr"/>
+      <c r="K912" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L912" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56137,7 +58713,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K913" t="inlineStr"/>
+      <c r="K913" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L913" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56198,7 +58778,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K914" t="inlineStr"/>
+      <c r="K914" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L914" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56381,7 +58965,11 @@
           <t>76.556.184-1</t>
         </is>
       </c>
-      <c r="K917" t="inlineStr"/>
+      <c r="K917" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L917" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56442,7 +59030,11 @@
           <t>77.499.324-K</t>
         </is>
       </c>
-      <c r="K918" t="inlineStr"/>
+      <c r="K918" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L918" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56503,7 +59095,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K919" t="inlineStr"/>
+      <c r="K919" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L919" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56564,7 +59160,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K920" t="inlineStr"/>
+      <c r="K920" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L920" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56686,7 +59286,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K922" t="inlineStr"/>
+      <c r="K922" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L922" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56747,7 +59351,11 @@
           <t>76.299.358-9</t>
         </is>
       </c>
-      <c r="K923" t="inlineStr"/>
+      <c r="K923" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L923" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56808,7 +59416,11 @@
           <t>96.556.940-5</t>
         </is>
       </c>
-      <c r="K924" t="inlineStr"/>
+      <c r="K924" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L924" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56869,7 +59481,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K925" t="inlineStr"/>
+      <c r="K925" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L925" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56930,7 +59546,11 @@
           <t>89.842.300-k</t>
         </is>
       </c>
-      <c r="K926" t="inlineStr"/>
+      <c r="K926" t="inlineStr">
+        <is>
+          <t>Biobío</t>
+        </is>
+      </c>
       <c r="L926" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56991,7 +59611,11 @@
           <t>96.670.840-9</t>
         </is>
       </c>
-      <c r="K927" t="inlineStr"/>
+      <c r="K927" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L927" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/articulos-de-aseo-e-higiene/ago-2026.xlsx
+++ b/docs/oc-mensuales/articulos-de-aseo-e-higiene/ago-2026.xlsx
@@ -2724,7 +2724,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3110,7 +3114,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4654,7 +4662,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5857,7 +5869,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5918,7 +5934,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7657,7 +7677,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11204,7 +11228,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11582,7 +11610,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11895,7 +11927,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11956,7 +11992,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12147,7 +12187,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12529,7 +12573,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15629,7 +15677,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr"/>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L237" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15885,7 +15937,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16393,7 +16449,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16454,7 +16514,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr"/>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L250" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16958,7 +17022,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17019,7 +17087,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr"/>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L259" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17271,7 +17343,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr"/>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L263" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17580,7 +17656,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr"/>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L268" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21119,7 +21199,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K323" t="inlineStr"/>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L323" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22184,7 +22268,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K340" t="inlineStr"/>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L340" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22753,7 +22841,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K349" t="inlineStr"/>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L349" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23001,7 +23093,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K353" t="inlineStr"/>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L353" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23188,7 +23284,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K356" t="inlineStr"/>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L356" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24732,7 +24832,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K380" t="inlineStr"/>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L380" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25366,7 +25470,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K390" t="inlineStr"/>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L390" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27101,7 +27209,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K417" t="inlineStr"/>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L417" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27613,7 +27725,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K425" t="inlineStr"/>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L425" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28751,7 +28867,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K443" t="inlineStr"/>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L443" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28942,7 +29062,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K446" t="inlineStr"/>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L446" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29194,7 +29318,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K450" t="inlineStr"/>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L450" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31108,7 +31236,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K480" t="inlineStr"/>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L480" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31685,7 +31817,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K489" t="inlineStr"/>
+      <c r="K489" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L489" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31937,7 +32073,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K493" t="inlineStr"/>
+      <c r="K493" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L493" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32319,7 +32459,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K499" t="inlineStr"/>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L499" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32640,7 +32784,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K504" t="inlineStr"/>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L504" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32823,7 +32971,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K507" t="inlineStr"/>
+      <c r="K507" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L507" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34229,7 +34381,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K529" t="inlineStr"/>
+      <c r="K529" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L529" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35119,7 +35275,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K543" t="inlineStr"/>
+      <c r="K543" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L543" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35241,7 +35401,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K545" t="inlineStr"/>
+      <c r="K545" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L545" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35432,7 +35596,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K548" t="inlineStr"/>
+      <c r="K548" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L548" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35623,7 +35791,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K551" t="inlineStr"/>
+      <c r="K551" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L551" t="inlineStr">
         <is>
           <t>USD</t>
@@ -35814,7 +35986,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K554" t="inlineStr"/>
+      <c r="K554" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L554" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36066,7 +36242,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K558" t="inlineStr"/>
+      <c r="K558" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L558" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36127,7 +36307,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K559" t="inlineStr"/>
+      <c r="K559" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L559" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36513,7 +36697,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K565" t="inlineStr"/>
+      <c r="K565" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L565" t="inlineStr">
         <is>
           <t>USD</t>
@@ -36574,7 +36762,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K566" t="inlineStr"/>
+      <c r="K566" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L566" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37151,7 +37343,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K575" t="inlineStr"/>
+      <c r="K575" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L575" t="inlineStr">
         <is>
           <t>USD</t>
@@ -37533,7 +37729,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K581" t="inlineStr"/>
+      <c r="K581" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L581" t="inlineStr">
         <is>
           <t>USD</t>
@@ -38240,7 +38440,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K592" t="inlineStr"/>
+      <c r="K592" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L592" t="inlineStr">
         <is>
           <t>USD</t>
@@ -39008,7 +39212,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K604" t="inlineStr"/>
+      <c r="K604" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L604" t="inlineStr">
         <is>
           <t>USD</t>
@@ -40995,7 +41203,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K635" t="inlineStr"/>
+      <c r="K635" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L635" t="inlineStr">
         <is>
           <t>USD</t>
@@ -41499,7 +41711,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K643" t="inlineStr"/>
+      <c r="K643" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L643" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42328,7 +42544,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K656" t="inlineStr"/>
+      <c r="K656" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L656" t="inlineStr">
         <is>
           <t>USD</t>
@@ -42645,7 +42865,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K661" t="inlineStr"/>
+      <c r="K661" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L661" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43352,7 +43576,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K672" t="inlineStr"/>
+      <c r="K672" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L672" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43543,7 +43771,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K675" t="inlineStr"/>
+      <c r="K675" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L675" t="inlineStr">
         <is>
           <t>USD</t>
@@ -43799,7 +44031,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K679" t="inlineStr"/>
+      <c r="K679" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L679" t="inlineStr">
         <is>
           <t>USD</t>
@@ -44957,7 +45193,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K697" t="inlineStr"/>
+      <c r="K697" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L697" t="inlineStr">
         <is>
           <t>USD</t>
@@ -46172,7 +46412,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K716" t="inlineStr"/>
+      <c r="K716" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L716" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47066,7 +47310,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K730" t="inlineStr"/>
+      <c r="K730" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L730" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47127,7 +47375,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K731" t="inlineStr"/>
+      <c r="K731" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L731" t="inlineStr">
         <is>
           <t>USD</t>
@@ -47249,7 +47501,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K733" t="inlineStr"/>
+      <c r="K733" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L733" t="inlineStr">
         <is>
           <t>USD</t>
@@ -48846,7 +49102,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K758" t="inlineStr"/>
+      <c r="K758" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L758" t="inlineStr">
         <is>
           <t>USD</t>
@@ -49224,7 +49484,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K764" t="inlineStr"/>
+      <c r="K764" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L764" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50378,7 +50642,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K782" t="inlineStr"/>
+      <c r="K782" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L782" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50439,7 +50707,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K783" t="inlineStr"/>
+      <c r="K783" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L783" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50500,7 +50772,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K784" t="inlineStr"/>
+      <c r="K784" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L784" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50752,7 +51028,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K788" t="inlineStr"/>
+      <c r="K788" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L788" t="inlineStr">
         <is>
           <t>USD</t>
@@ -50874,7 +51154,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K790" t="inlineStr"/>
+      <c r="K790" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L790" t="inlineStr">
         <is>
           <t>USD</t>
@@ -51191,7 +51475,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K795" t="inlineStr"/>
+      <c r="K795" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L795" t="inlineStr">
         <is>
           <t>USD</t>
@@ -52780,7 +53068,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K820" t="inlineStr"/>
+      <c r="K820" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L820" t="inlineStr">
         <is>
           <t>USD</t>
@@ -53739,7 +54031,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K835" t="inlineStr"/>
+      <c r="K835" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L835" t="inlineStr">
         <is>
           <t>USD</t>
@@ -54442,7 +54738,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K846" t="inlineStr"/>
+      <c r="K846" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L846" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55210,7 +55510,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K858" t="inlineStr"/>
+      <c r="K858" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L858" t="inlineStr">
         <is>
           <t>USD</t>
@@ -55592,7 +55896,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K864" t="inlineStr"/>
+      <c r="K864" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L864" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56234,7 +56542,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K874" t="inlineStr"/>
+      <c r="K874" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L874" t="inlineStr">
         <is>
           <t>USD</t>
@@ -56356,7 +56668,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K876" t="inlineStr"/>
+      <c r="K876" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L876" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57185,7 +57501,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K889" t="inlineStr"/>
+      <c r="K889" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L889" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57441,7 +57761,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K893" t="inlineStr"/>
+      <c r="K893" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L893" t="inlineStr">
         <is>
           <t>USD</t>
@@ -57953,7 +58277,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K901" t="inlineStr"/>
+      <c r="K901" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L901" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58014,7 +58342,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K902" t="inlineStr"/>
+      <c r="K902" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L902" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58522,7 +58854,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K910" t="inlineStr"/>
+      <c r="K910" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L910" t="inlineStr">
         <is>
           <t>USD</t>
@@ -58904,7 +59240,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K916" t="inlineStr"/>
+      <c r="K916" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L916" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59225,7 +59565,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K921" t="inlineStr"/>
+      <c r="K921" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L921" t="inlineStr">
         <is>
           <t>USD</t>
@@ -59676,7 +60020,11 @@
           <t>76.287.853-4</t>
         </is>
       </c>
-      <c r="K928" t="inlineStr"/>
+      <c r="K928" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L928" t="inlineStr">
         <is>
           <t>USD</t>
